--- a/23127060/testcases/23127060_HW06_testcases.xlsx
+++ b/23127060/testcases/23127060_HW06_testcases.xlsx
@@ -953,7 +953,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>POST /api/forgot-password | email = api.victim.23127060@test.local (email ton tai)</t>
+          <t>POST /api/forgot-password | email = api.victim.23127060@test.local (email tồn tại)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>User api.victim.23127060@test.local da ton tai</t>
+          <t>User api.victim.23127060@test.local đã tồn tại</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>body co message; body KHONG chua resetToken</t>
+          <t>body có message; body KHÔNG chứa resetToken</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>POST /api/forgot-password | email = khongtontai.23127060@test.local (email khong ton tai - khong duoc lo user enumeration)</t>
+          <t>POST /api/forgot-password | email = khongtontai.23127060@test.local (email không tồn tại - không được lộ user enumeration)</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>User api.victim.23127060@test.local da ton tai</t>
+          <t>User api.victim.23127060@test.local đã tồn tại</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>tra ve thong diep chung chung giong truong hop ton tai</t>
+          <t>trả về thông điệp chung chung giống trường hợp tồn tại</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>R6 - Ky vong 'email khong ton tai van tra 200 (chong user enumeration)' KHONG duoc SRS phat bieu truc tiep; day la suy dien tu thong le. DA SUA: ghi ro Oracle = SPEC(suy dien) de nguoi cham phan biet duoc voi cac ky vong trich thang tu dac ta.</t>
+          <t>R6 - Kỳ vọng 'email không tồn tại vẫn trả 200 (chống user enumeration)' KHÔNG được SRS phát biểu trực tiếp; đây là suy diễn từ thông lệ. ĐÃ SỬA: ghi rõ Oracle = SPEC(suy diễn) để người chấm phân biệt được với các kỳ vọng trích thẳng từ đặc tả.</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>POST /api/forgot-password | email =  (email rong)</t>
+          <t>POST /api/forgot-password | email =  (email rỗng)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>User api.victim.23127060@test.local da ton tai</t>
+          <t>User api.victim.23127060@test.local đã tồn tại</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>POST /api/forgot-password | email = &lt;thieu key&gt; (thieu key email)</t>
+          <t>POST /api/forgot-password | email = &lt;thieu key&gt; (thiếu key email)</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>User api.victim.23127060@test.local da ton tai</t>
+          <t>User api.victim.23127060@test.local đã tồn tại</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>User api.victim.23127060@test.local da ton tai</t>
+          <t>User api.victim.23127060@test.local đã tồn tại</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>POST /api/forgot-password | email = 12345 (email sai kieu (number))</t>
+          <t>POST /api/forgot-password | email = 12345 (email sai kiểu (number))</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>User api.victim.23127060@test.local da ton tai</t>
+          <t>User api.victim.23127060@test.local đã tồn tại</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>POST /api/forgot-password | email = abc@@test (email sai dinh dang)</t>
+          <t>POST /api/forgot-password | email = abc@@test (email sai định dạng)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>User api.victim.23127060@test.local da ton tai</t>
+          <t>User api.victim.23127060@test.local đã tồn tại</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>POST /api/forgot-password | email = aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa (BVA - email vuot 254 ky tu)</t>
+          <t>POST /api/forgot-password | email = aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa (BVA - email vượt 254 ký tự)</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>User api.victim.23127060@test.local da ton tai</t>
+          <t>User api.victim.23127060@test.local đã tồn tại</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>POST /api/forgot-password | email = API.VICTIM.23127060@TEST.LOCAL (email khac hoa thuong - phai coi la cung 1 user)</t>
+          <t>POST /api/forgot-password | email = API.VICTIM.23127060@TEST.LOCAL (email khác hoa thường - phải coi là cùng 1 user)</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>User api.victim.23127060@test.local da ton tai</t>
+          <t>User api.victim.23127060@test.local đã tồn tại</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; khop schema thanh cong</t>
+          <t>body là JSON; khớp schema thành công</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>R6 - Ky vong 'email khong phan biet hoa thuong' KHONG duoc SRS phat bieu truc tiep; day la suy dien tu thong le. DA SUA: ghi ro Oracle = SPEC(suy dien) de nguoi cham phan biet duoc voi cac ky vong trich thang tu dac ta.</t>
+          <t>R6 - Kỳ vọng 'email không phân biệt hoa thường' KHÔNG được SRS phát biểu trực tiếp; đây là suy diễn từ thông lệ. ĐÃ SỬA: ghi rõ Oracle = SPEC(suy diễn) để người chấm phân biệt được với các kỳ vọng trích thẳng từ đặc tả.</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>POST /api/forgot-password | email =   api.victim.23127060@test.local   (email co khoang trang thua - phai trim)</t>
+          <t>POST /api/forgot-password | email =   api.victim.23127060@test.local   (email có khoảng trắng thừa - phải trim)</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>User api.victim.23127060@test.local da ton tai</t>
+          <t>User api.victim.23127060@test.local đã tồn tại</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; khop schema thanh cong</t>
+          <t>body là JSON; khớp schema thành công</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>R6 - Ky vong 'email tu cat khoang trang dau-cuoi' KHONG duoc SRS phat bieu truc tiep; day la suy dien tu thong le. DA SUA: ghi ro Oracle = SPEC(suy dien) de nguoi cham phan biet duoc voi cac ky vong trich thang tu dac ta.</t>
+          <t>R6 - Kỳ vọng 'email tu cat khoang trang dau-cuoi' KHÔNG được SRS phát biểu trực tiếp; đây là suy diễn từ thông lệ. ĐÃ SỬA: ghi rõ Oracle = SPEC(suy diễn) để người chấm phân biệt được với các kỳ vọng trích thẳng từ đặc tả.</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>User api.victim.23127060@test.local da ton tai</t>
+          <t>User api.victim.23127060@test.local đã tồn tại</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>POST /api/reset-password | email = api.victim.23127060@test.local (email dung chu token)</t>
+          <t>POST /api/reset-password | email = api.victim.23127060@test.local (email đúng chứ token)</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Da goi forgot-password va co {{resetToken}}</t>
+          <t>Đã gọi forgot-password và có {{resetToken}}</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>body co message; login bang mat khau moi thanh cong; login bang mat khau cu that bai</t>
+          <t>body có message; login bằng mật khẩu mới thành công; login bằng mật khẩu cũ thất bại</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>POST /api/reset-password | email = api.attacker.23127060@test.local (dung token cua user khac)</t>
+          <t>POST /api/reset-password | email = api.attacker.23127060@test.local (dùng token của user khác)</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Da goi forgot-password va co {{resetToken}}</t>
+          <t>Đã gọi forgot-password và có {{resetToken}}</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>R3 - Gan sai ma SEC (SEC-04 -&gt; SEC-07). Dung OTP cua tai khoan khac chinh la dieu SEC-07 + FR-03 quy dinh ('OTP chi hop le cho email da yeu cau'), khong phai SEC-04 (escape XSS).</t>
+          <t>R3 - Gan sai ma SEC (SEC-04 -&gt; SEC-07). Dùng OTP của tài khoản khác chính là điều SEC-07 + FR-03 quy định ('OTP chỉ hợp lệ cho email đã yêu cầu'), không phải SEC-04 (escape XSS).</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>POST /api/reset-password | email = &lt;thieu key&gt; (thieu key email)</t>
+          <t>POST /api/reset-password | email = &lt;thieu key&gt; (thiếu key email)</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Da goi forgot-password va co {{resetToken}}</t>
+          <t>Đã gọi forgot-password và có {{resetToken}}</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Da goi forgot-password va co {{resetToken}}</t>
+          <t>Đã gọi forgot-password và có {{resetToken}}</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Da goi forgot-password va co {{resetToken}}</t>
+          <t>Đã gọi forgot-password và có {{resetToken}}</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>POST /api/reset-password | resetToken =  (token rong)</t>
+          <t>POST /api/reset-password | resetToken =  (token rỗng)</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Da goi forgot-password va co {{resetToken}}</t>
+          <t>Đã gọi forgot-password và có {{resetToken}}</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>POST /api/reset-password | resetToken = &lt;thieu key&gt; (thieu token)</t>
+          <t>POST /api/reset-password | resetToken = &lt;thieu key&gt; (thiếu token)</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Da goi forgot-password va co {{resetToken}}</t>
+          <t>Đã gọi forgot-password và có {{resetToken}}</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Da goi forgot-password va co {{resetToken}}</t>
+          <t>Đã gọi forgot-password và có {{resetToken}}</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>POST /api/reset-password | resetToken = 123 (BVA - token 3 ky tu (duoi bien))</t>
+          <t>POST /api/reset-password | resetToken = 123 (BVA - token 3 ký tự (dưới biên))</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Da goi forgot-password va co {{resetToken}}</t>
+          <t>Đã gọi forgot-password và có {{resetToken}}</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>R6 - Ky vong 'do dai OTP duoi bien' KHONG duoc SRS phat bieu truc tiep; day la suy dien tu thong le. DA SUA: ghi ro Oracle = SPEC(suy dien) de nguoi cham phan biet duoc voi cac ky vong trich thang tu dac ta.</t>
+          <t>R6 - Kỳ vọng 'do dai OTP duoi bien' KHÔNG được SRS phát biểu trực tiếp; đây là suy diễn từ thông lệ. ĐÃ SỬA: ghi rõ Oracle = SPEC(suy diễn) để người chấm phân biệt được với các kỳ vọng trích thẳng từ đặc tả.</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>POST /api/reset-password | resetToken = 12345 (BVA - token 5 ky tu (tren bien))</t>
+          <t>POST /api/reset-password | resetToken = 12345 (BVA - token 5 ký tự (trên biên))</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Da goi forgot-password va co {{resetToken}}</t>
+          <t>Đã gọi forgot-password và có {{resetToken}}</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>R6 - Ky vong 'do dai OTP tren bien' KHONG duoc SRS phat bieu truc tiep; day la suy dien tu thong le. DA SUA: ghi ro Oracle = SPEC(suy dien) de nguoi cham phan biet duoc voi cac ky vong trich thang tu dac ta.</t>
+          <t>R6 - Kỳ vọng 'do dai OTP tren bien' KHÔNG được SRS phát biểu trực tiếp; đây là suy diễn từ thông lệ. ĐÃ SỬA: ghi rõ Oracle = SPEC(suy diễn) để người chấm phân biệt được với các kỳ vọng trích thẳng từ đặc tả.</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>POST /api/reset-password | resetToken = ' OR '1'='1 (token chua SQLi)</t>
+          <t>POST /api/reset-password | resetToken = ' OR '1'='1 (token chứa SQLi)</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Da goi forgot-password va co {{resetToken}}</t>
+          <t>Đã gọi forgot-password và có {{resetToken}}</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>R3 - Gan sai ma SEC (SEC-01 -&gt; SEC-05). SQLi -&gt; SEC-05 (parameterized query), khong phai SEC-01 (luu mat khau plaintext).</t>
+          <t>R3 - Gan sai ma SEC (SEC-01 -&gt; SEC-05). SQLi -&gt; SEC-05 (parameterized query), không phải SEC-01 (lưu mật khẩu plaintext).</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>POST /api/reset-password | resetToken = 1234 (token sai kieu (number))</t>
+          <t>POST /api/reset-password | resetToken = 1234 (token sai kiểu (number))</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Da goi forgot-password va co {{resetToken}}</t>
+          <t>Đã gọi forgot-password và có {{resetToken}}</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>POST /api/reset-password | resetToken = {{oldResetToken}} (token cu sau khi xin token moi - phai het hieu luc)</t>
+          <t>POST /api/reset-password | resetToken = {{oldResetToken}} (token cũ sau khi xin token mới - phải hết hiệu lực)</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Da goi forgot-password va co {{resetToken}}</t>
+          <t>Đã gọi forgot-password và có {{resetToken}}</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>POST /api/reset-password | newPassword = NewApi1234! (mat khau manh hop le)</t>
+          <t>POST /api/reset-password | newPassword = NewApi1234! (mật khẩu mạnh hợp lệ)</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Da goi forgot-password va co {{resetToken}}</t>
+          <t>Đã gọi forgot-password và có {{resetToken}}</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; khop schema thanh cong; VA doc lai tai nguyen de xac nhan gia tri luu dung bang gia tri da gui</t>
+          <t>body là JSON; khớp schema thành công; VA doc lai tai nguyen de xac nhan gia tri luu dung bang gia tri da gui</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>R8 - Case thanh cong nhung chi kiem 'khop schema'. Thieu khang dinh gia tri that su duoc luu dung. DA SUA: bo sung buoc doc lai tai nguyen va so khop gia tri vua gui.</t>
+          <t>R8 - Case thành công nhưng chỉ kiểm 'khớp schema'. Thiếu khẳng định giá trị thật sự được lưu đúng. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên và so khớp giá trị vừa gửi.</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>POST /api/reset-password | newPassword =  (mat khau rong)</t>
+          <t>POST /api/reset-password | newPassword =  (mật khẩu rỗng)</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Da goi forgot-password va co {{resetToken}}</t>
+          <t>Đã gọi forgot-password và có {{resetToken}}</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>R3 - Gan sai ma SEC (SEC-06 -&gt; -). Do manh mat khau la yeu cau FR-01/FR-03, khong nam trong SEC-01..07. SEC-06 chi noi rieng ve truong role.</t>
+          <t>R3 - Gan sai ma SEC (SEC-06 -&gt; -). Độ mạnh mật khẩu là yêu cầu FR-01/FR-03, không nằm trong SEC-01..07. SEC-06 chỉ nói riêng về trường role.</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>POST /api/reset-password | newPassword = &lt;thieu key&gt; (thieu newPassword)</t>
+          <t>POST /api/reset-password | newPassword = &lt;thieu key&gt; (thiếu newPassword)</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Da goi forgot-password va co {{resetToken}}</t>
+          <t>Đã gọi forgot-password và có {{resetToken}}</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Da goi forgot-password va co {{resetToken}}</t>
+          <t>Đã gọi forgot-password và có {{resetToken}}</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>POST /api/reset-password | newPassword = Ab1234! (BVA - 7 ky tu (duoi bien toi thieu 8))</t>
+          <t>POST /api/reset-password | newPassword = Ab1234! (BVA - 7 ký tự (dưới biên tối thiểu 8))</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Da goi forgot-password va co {{resetToken}}</t>
+          <t>Đã gọi forgot-password và có {{resetToken}}</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>R3 - Gan sai ma SEC (SEC-06 -&gt; -). Nhu tren: do dai mat khau la FR-01, khong phai ma SEC.</t>
+          <t>R3 - Gan sai ma SEC (SEC-06 -&gt; -). Như trên: độ dài mật khẩu là FR-01, không phải mã SEC.</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>POST /api/reset-password | newPassword = Ab1234!x (BVA - dung 8 ky tu)</t>
+          <t>POST /api/reset-password | newPassword = Ab1234!x (BVA - đúng 8 ký tự)</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Da goi forgot-password va co {{resetToken}}</t>
+          <t>Đã gọi forgot-password và có {{resetToken}}</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; khop schema thanh cong; VA doc lai tai nguyen de xac nhan gia tri luu dung bang gia tri da gui</t>
+          <t>body là JSON; khớp schema thành công; VA doc lai tai nguyen de xac nhan gia tri luu dung bang gia tri da gui</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>R8 - Case thanh cong nhung chi kiem 'khop schema'. Thieu khang dinh gia tri that su duoc luu dung. DA SUA: bo sung buoc doc lai tai nguyen va so khop gia tri vua gui.</t>
+          <t>R8 - Case thành công nhưng chỉ kiểm 'khớp schema'. Thiếu khẳng định giá trị thật sự được lưu đúng. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên và so khớp giá trị vừa gửi.</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>POST /api/reset-password | newPassword = abcd1234! (thieu chu hoa)</t>
+          <t>POST /api/reset-password | newPassword = abcd1234! (thiếu chữ hoa)</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Da goi forgot-password va co {{resetToken}}</t>
+          <t>Đã gọi forgot-password và có {{resetToken}}</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>POST /api/reset-password | newPassword = Abcdefgh! (thieu chu so)</t>
+          <t>POST /api/reset-password | newPassword = Abcdefgh! (thiếu chữ số)</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Da goi forgot-password va co {{resetToken}}</t>
+          <t>Đã gọi forgot-password và có {{resetToken}}</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>POST /api/reset-password | newPassword = 123456 (mat khau qua yeu pho bien)</t>
+          <t>POST /api/reset-password | newPassword = 123456 (mật khẩu quá yếu phổ biến)</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Da goi forgot-password va co {{resetToken}}</t>
+          <t>Đã gọi forgot-password và có {{resetToken}}</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>R3 - Gan sai ma SEC (SEC-06 -&gt; -). Nhu tren: mat khau yeu vi pham FR-01, khong phai ma SEC.</t>
+          <t>R3 - Gan sai ma SEC (SEC-06 -&gt; -). Như trên: mật khẩu yếu vi phạm FR-01, không phải mã SEC.</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>POST /api/reset-password | newPassword = &lt;script&gt;alert(1)&lt;/script&gt; (payload XSS lam mat khau)</t>
+          <t>POST /api/reset-password | newPassword = &lt;script&gt;alert(1)&lt;/script&gt; (payload XSS làm mật khẩu)</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Da goi forgot-password va co {{resetToken}}</t>
+          <t>Đã gọi forgot-password và có {{resetToken}}</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>POST /api/reset-password | newPassword = Api1234! (dat lai trung mat khau cu - SRS khong cam)</t>
+          <t>POST /api/reset-password | newPassword = Api1234! (đặt lại trùng mật khẩu cũ - SRS không cấm)</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Da goi forgot-password va co {{resetToken}}</t>
+          <t>Đã gọi forgot-password và có {{resetToken}}</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>reset thanh cong; SRS khong cam dat lai trung mat khau cu; login bang mat khau do phai thanh cong</t>
+          <t>reset thành công; SRS không cấm đặt lại trùng mật khẩu cũ; login bằng mật khẩu đó phải thành công</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>R3b - Ky vong 400 khong co can cu: SRS FR-01/FR-03 chi doi mat khau moi THOA DIEU KIEN DO MANH, khong he cam dat lai trung mat khau cu. AI ap mot chinh sach ma dac ta khong co. DA SUA: ky vong 200, va them khang dinh mat khau cu van dang nhap duoc (vi no chinh la mat khau moi).</t>
+          <t>R3b - Kỳ vọng 400 không có căn cứ: SRS FR-01/FR-03 chỉ đòi mật khẩu mới THỎA ĐIỀU KIỆN ĐỘ MẠNH, không hề cấm đặt lại trùng mật khẩu cũ. AI áp một chính sách mà đặc tả không có. ĐÃ SỬA: kỳ vọng 200, và thêm khẳng định mật khẩu cũ vẫn đăng nhập được (vì nó chính là mật khẩu mới).</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>POST /api/reset-password | newPassword = A1!aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa (BVA - vuot do dai toi da 128)</t>
+          <t>POST /api/reset-password | newPassword = A1!aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa (BVA - vượt độ dài tối đa 128)</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Da goi forgot-password va co {{resetToken}}</t>
+          <t>Đã gọi forgot-password và có {{resetToken}}</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai NONE -&gt; USED (KHONG hop le)</t>
+          <t>Chuyển trạng thái NONE -&gt; USED (KHÔNG hợp lệ)</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>Doi tuong dang o trang thai NONE. Chua goi forgot-password lan nao</t>
+          <t>Đối tượng đang ở trạng thái NONE. Chua goi forgot-password lan nao</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>body.error co gia tri; mat khau KHONG doi</t>
+          <t>body.error có giá trị; mật khẩu KHÔNG đổi</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai NONE -&gt; ISSUED (hop le)</t>
+          <t>Chuyển trạng thái NONE -&gt; ISSUED (hợp lệ)</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doi tuong dang o trang thai NONE. </t>
+          <t xml:space="preserve">Đối tượng đang ở trạng thái NONE. </t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>token duoc tao va gui qua kenh ngoai band; KHONG tra trong response</t>
+          <t>token được tạo và gửi qua kênh ngoài băng; KHÔNG trả trong response</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai ISSUED -&gt; USED (hop le)</t>
+          <t>Chuyển trạng thái ISSUED -&gt; USED (hợp lệ)</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doi tuong dang o trang thai ISSUED. </t>
+          <t xml:space="preserve">Đối tượng đang ở trạng thái ISSUED. </t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>reset_token bi xoa; login bang mat khau moi OK</t>
+          <t>reset_token bị xóa; login bằng mật khẩu mới OK</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai USED -&gt; USED (KHONG hop le)</t>
+          <t>Chuyển trạng thái USED -&gt; USED (KHÔNG hợp lệ)</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>Doi tuong dang o trang thai USED. Token da dung 1 lan</t>
+          <t>Đối tượng đang ở trạng thái USED. Token đã dùng 1 lần</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>token dung 1 lan duy nhat</t>
+          <t>token dùng 1 lần duy nhất</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai ISSUED -&gt; ISSUED (hop le)</t>
+          <t>Chuyển trạng thái ISSUED -&gt; ISSUED (hợp lệ)</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>Doi tuong dang o trang thai ISSUED. Da co token, xin token moi</t>
+          <t>Đối tượng đang ở trạng thái ISSUED. Đã có token, xin token mới</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>token cu phai bi vo hieu hoa</t>
+          <t>token cũ phải bị vô hiệu hóa</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai USED -&gt; USED (dung lai OTP da dung - KHONG hop le)</t>
+          <t>Chuyển trạng thái USED -&gt; USED (dùng lại OTP đã dùng - KHÔNG hợp lệ)</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>Da reset mat khau thanh cong mot lan bang OTP nay</t>
+          <t>Đã reset mật khẩu thành công một lần bằng OTP này</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>lan reset thu hai voi cung OTP phai bi tu choi; body co truong error</t>
+          <t>lần reset thứ hai với cùng OTP phải bị từ chối; body có trường error</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t>R4 - Mau thuan noi tai: case danh dau chuyen trang thai HOP LE nhung lai ky vong 400. Ngoai ra 'EXPIRED' khong phai mot trang thai ma bo sinh dieu khien duoc: SUT khong luu thoi diem cap OTP nen khong the dua OTP ve trang thai het han qua API. DA SUA: doi thanh chuyen KHONG hop le ISSUED -&gt; USED_TWICE (dung lai OTP da dung), la dieu SEC-07 quy dinh ro va kiem duoc hoan toan qua API.</t>
+          <t>R4 - Mâu thuẫn nội tại: case đánh dấu chuyển trạng thái HỢP LỆ nhưng lại kỳ vọng 400. Ngoài ra 'EXPIRED' không phải một trạng thái mà bộ sinh điều khiển được: SUT không lưu thời điểm cấp OTP nên không thể đưa OTP về trạng thái hết hạn qua API. ĐÃ SỬA: đổi thành chuyển KHÔNG hợp lệ ISSUED -&gt; USED_TWICE (dùng lại OTP đã dùng), là điều SEC-07 quy định rõ và kiểm được hoàn toàn qua API.</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai LOCKED -&gt; USED (hop le)</t>
+          <t>Chuyển trạng thái LOCKED -&gt; USED (hợp lệ)</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>Doi tuong dang o trang thai LOCKED. Tai khoan dang bi khoa do login sai 3 lan</t>
+          <t>Đối tượng đang ở trạng thái LOCKED. Tài khoản đang bị khóa do login sai 3 lần</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>sau khi reset, login_attempts=0 va locked_until=NULL; login duoc ngay</t>
+          <t>sau khi reset, login_attempts=0 và locked_until=NULL; login được ngay</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai USED -&gt; LOGIN_OLD (KHONG hop le)</t>
+          <t>Chuyển trạng thái USED -&gt; LOGIN_OLD (KHÔNG hợp lệ)</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>Doi tuong dang o trang thai USED. Da reset mat khau thanh cong</t>
+          <t>Đối tượng đang ở trạng thái USED. Đã reset mật khẩu thành công</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>mat khau cu khong con dung duoc</t>
+          <t>mật khẩu cũ không còn dùng được</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai USED -&gt; LOGIN_NEW (hop le)</t>
+          <t>Chuyển trạng thái USED -&gt; LOGIN_NEW (hợp lệ)</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>Doi tuong dang o trang thai USED. Da reset mat khau thanh cong</t>
+          <t>Đối tượng đang ở trạng thái USED. Đã reset mật khẩu thành công</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>tra ve token JWT; body KHONG chua truong password</t>
+          <t>trả về token JWT; body KHÔNG chứa trường password</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>[SEC-05] SQLi qua truong email cua forgot-password</t>
+          <t>[SEC-05] SQLi qua trường email của forgot-password</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>response KHONG chua truong password (du plaintext hay hash); mat khau khong duoc luu plaintext</t>
+          <t>response KHÔNG chứa trường password (dù plaintext hay hash); mật khẩu không được lưu plaintext</t>
         </is>
       </c>
       <c r="N47" s="4" t="inlineStr">
@@ -5878,7 +5878,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>R3 - Gan sai ma SEC (SEC-01 -&gt; SEC-05). SQLi la vi pham SEC-05 (parameterized query), khong phai SEC-01 (luu mat khau plaintext).</t>
+          <t>R3 - Gan sai ma SEC (SEC-01 -&gt; SEC-05). SQLi là vi phạm SEC-05 (parameterized query), không phải SEC-01 (lưu mật khẩu plaintext).</t>
         </is>
       </c>
       <c r="T47" s="4" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>[SEC-05] SQLi qua resetToken de bypass kiem tra token</t>
+          <t>[SEC-05] SQLi qua resetToken để bypass kiểm tra token</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>mat khau KHONG bi doi; kiem tra bang cach login lai bang mat khau cu</t>
+          <t>mật khẩu KHÔNG bị đổi; kiểm tra bằng cách login lại bằng mật khẩu cũ</t>
         </is>
       </c>
       <c r="N48" s="4" t="inlineStr">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>[SEC-07] Response cua forgot-password khong duoc chua resetToken</t>
+          <t>[SEC-07] Response của forgot-password không được chứa resetToken</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>body KHONG co truong resetToken; body KHONG co truong password</t>
+          <t>body KHÔNG có trường resetToken; body KHÔNG có trường password</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>R3 - Gan sai ma SEC (SEC-02 -&gt; SEC-07). Tra thang OTP ra response la loi vong doi OTP -&gt; SEC-07, khong phai SEC-02 (yeu cau JWT).</t>
+          <t>R3 - Gan sai ma SEC (SEC-02 -&gt; SEC-07). Trả thẳng OTP ra response là lỗi vòng đời OTP -&gt; SEC-07, không phải SEC-02 (yêu cầu JWT).</t>
         </is>
       </c>
       <c r="T49" s="4" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>[-] Thong diep phai giong nhau giua email ton tai va khong ton tai</t>
+          <t>[-] Thông điệp phải giống nhau giữa email tồn tại và không tồn tại</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
@@ -6172,7 +6172,7 @@
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>status va message giong het truong hop email ton tai</t>
+          <t>status và message giống hệt trường hợp email tồn tại</t>
         </is>
       </c>
       <c r="N50" s="4" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>R3 - Gan sai ma SEC (SEC-02 -&gt; -). User enumeration KHONG duoc bat ky ma SEC-01..07 nao phu. Van la test hop le nhung phai de SEC_Ref = '-' thay vi gan bua.</t>
+          <t>R3 - Gan sai ma SEC (SEC-02 -&gt; -). User enumeration KHÔNG được bất kỳ mã SEC-01..07 nào phủ. Vẫn là test hợp lệ nhưng phải để SEC_Ref = '-' thay vì gán bừa.</t>
         </is>
       </c>
       <c r="T50" s="4" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>[SEC-01] Response cua login khong duoc chua hash/plaintext mat khau</t>
+          <t>[SEC-01] Response của login không được chứa hash/plaintext mật khẩu</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>body.user KHONG co truong password</t>
+          <t>body.user KHÔNG có trường password</t>
         </is>
       </c>
       <c r="N51" s="4" t="inlineStr">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>R3 - Gan sai ma SEC (SEC-02 -&gt; SEC-01). Response login lo truong password chinh la bang chung mat khau duoc luu plaintext -&gt; dung SEC-01.</t>
+          <t>R3 - Gan sai ma SEC (SEC-02 -&gt; SEC-01). Response login lộ trường password chính là bằng chứng mật khẩu được lưu plaintext -&gt; đúng SEC-01.</t>
         </is>
       </c>
       <c r="T51" s="4" t="inlineStr">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>[SEC-07] Reset password khong duoc chap nhan khi thieu ca token lan xac thuc</t>
+          <t>[SEC-07] Reset password không được chấp nhận khi thiếu cả token lẫn xác thực</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t>tra 403 khi token hop le nhung role != 'admin'; hanh dong admin KHONG duoc thuc hien</t>
+          <t>trả 403 khi token hợp lệ nhưng role != 'admin'; hành động admin KHÔNG được thực hiện</t>
         </is>
       </c>
       <c r="N52" s="4" t="inlineStr">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>R3 - Gan sai ma SEC (SEC-03 -&gt; SEC-07). Reset phai doi OTP hop le -&gt; thuoc vong doi OTP SEC-07, khong phai SEC-03 (kiem role admin).</t>
+          <t>R3 - Gan sai ma SEC (SEC-03 -&gt; SEC-07). Reset phải đòi OTP hợp lệ -&gt; thuộc vòng đời OTP SEC-07, không phải SEC-03 (kiểm role admin).</t>
         </is>
       </c>
       <c r="T52" s="4" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>[SEC-07] Dung token cua user A de doi mat khau user B</t>
+          <t>[SEC-07] Dùng token của user A để đổi mật khẩu user B</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>Attacker tu xin token cho chinh minh</t>
+          <t>Attacker tự xin token cho chính mình</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>mat khau cua victim KHONG doi</t>
+          <t>mật khẩu của victim KHÔNG đổi</t>
         </is>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>R3 - Gan sai ma SEC (SEC-04 -&gt; SEC-07). 'OTP chi hop le cho email da yeu cau' la yeu cau cua SEC-07 + FR-03, khong phai SEC-04 (escape XSS).</t>
+          <t>R3 - Gan sai ma SEC (SEC-04 -&gt; SEC-07). 'OTP chỉ hợp lệ cho email đã yêu cầu' là yêu cầu của SEC-07 + FR-03, không phải SEC-04 (escape XSS).</t>
         </is>
       </c>
       <c r="T53" s="4" t="inlineStr">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>[SEC-06] Reset password khong duoc cho phep gui kem truong role</t>
+          <t>[SEC-06] Reset password không được cho phép gửi kèm trường role</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="M54" s="4" t="inlineStr">
         <is>
-          <t>sau khi reset, GET /api/users/me tra role='user' chu KHONG phai 'admin'</t>
+          <t>sau khi reset, GET /api/users/me trả role='user' chứ KHÔNG phải 'admin'</t>
         </is>
       </c>
       <c r="N54" s="4" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>R3 - Gan sai ma SEC (SEC-05 -&gt; SEC-06). Gui kem truong role dung la SEC-06; SEC-05 la parameterized query.</t>
+          <t>R3 - Gan sai ma SEC (SEC-05 -&gt; SEC-06). Gửi kèm trường role đúng là SEC-06; SEC-05 là parameterized query.</t>
         </is>
       </c>
       <c r="T54" s="4" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>[SEC-04] Email chua payload XSS phai bi tu choi hoac escape</t>
+          <t>[SEC-04] Email chứa payload XSS phải bị từ chối hoặc escape</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>truong role trong body bi bo qua; role cua tai khoan sau khi goi van la 'user'</t>
+          <t>trường role trong body bị bỏ qua; role của tài khoản sau khi gọi vẫn là 'user'</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>R3 - Gan sai ma SEC (SEC-06 -&gt; SEC-04). Payload XSS thuoc SEC-04; SEC-06 chi noi rieng ve truong role.</t>
+          <t>R3 - Gan sai ma SEC (SEC-06 -&gt; SEC-04). Payload XSS thuộc SEC-04; SEC-06 chỉ nói riêng về trường role.</t>
         </is>
       </c>
       <c r="T55" s="4" t="inlineStr">
@@ -6785,7 +6785,7 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>[SEC-04] Path traversal trong email khong duoc gay loi 500</t>
+          <t>[SEC-04] Path traversal trong email không được gây lỗi 500</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>khong tra 500; khong lo stack trace</t>
+          <t>không trả 500; không lộ stack trace</t>
         </is>
       </c>
       <c r="N56" s="4" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>[SEC-07] Do 20 gia tri token: khong lan nao duoc chap nhan va OTP phai dai &gt;= 6 chu so</t>
+          <t>[SEC-07] Dò 20 giá trị token: không lần nào được chấp nhận và OTP phải dài &gt;= 6 chữ số</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>Chay bang Collection Runner voi data file postman/data/brute_force_tokens.csv</t>
+          <t>Chạy bằng Collection Runner với data file postman/data/brute_force_tokens.csv</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>moi lan do deu tra 400; do dai resetToken lay tu forgot-password phai &gt;= 6 ky tu theo SEC-07</t>
+          <t>mỗi lần dò đều trả 400; độ dài resetToken lấy từ forgot-password phải &gt;= 6 ký tự theo SEC-07</t>
         </is>
       </c>
       <c r="N57" s="4" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>R1 - Ky vong 429 khong co can cu: khong mot dong nao trong FR-01..FR-24 hay SEC-01..07 yeu cau rate limiting. AI suy ra tu thoi quen bao mat chung chu khong tu dac ta. DA SUA: giu nguyen kich ban do 20 gia tri (van la cach chung minh entropy yeu) nhung doi oracle sang dieu SRS THUC SU noi - SEC-07 doi OTP toi thieu 6 chu so: khang dinh do dai token &gt;= 6 va khong lan do nao duoc chap nhan.</t>
+          <t>R1 - Kỳ vọng 429 không có căn cứ: không một dòng nào trong FR-01..FR-24 hay SEC-01..07 yêu cầu rate limiting. AI suy ra từ thói quen bảo mật chung chứ không từ đặc tả. ĐÃ SỬA: giữ nguyên kịch bản dò 20 giá trị (vẫn là cách chứng minh entropy yếu) nhưng đổi oracle sang điều SRS THỰC SỰ nói - SEC-07 đòi OTP tối thiểu 6 chữ số: khẳng định độ dài token &gt;= 6 và không lần dò nào được chấp nhận.</t>
         </is>
       </c>
       <c r="T57" s="4" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>[-] Do mat khau login lien tiep phai bi khoa dung sau 3 lan</t>
+          <t>[-] Dò mật khẩu login liên tiếp phải bị khóa đúng sau 3 lần</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>Chay 3 lan lien tiep voi mat khau sai</t>
+          <t>Chạy 3 lần liên tiếp với mật khẩu sai</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>lan thu 3 moi bi khoa (khong duoc khoa som o lan thu 2 do login_attempts+2)</t>
+          <t>lần thứ 3 mới bị khóa (không được khóa sớm ở lần thứ 2 do login_attempts+2)</t>
         </is>
       </c>
       <c r="N58" s="4" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>R3 - Gan sai ma SEC (SEC-07 -&gt; -). Khoa tai khoan sau 3 lan sai la FR-02, khong nam trong SEC-01..07.</t>
+          <t>R3 - Gan sai ma SEC (SEC-07 -&gt; -). Khóa tài khoản sau 3 lần sai là FR-02, không nằm trong SEC-01..07.</t>
         </is>
       </c>
       <c r="T58" s="4" t="inlineStr">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>[SEC-07] Xin OTP lan 2 thi OTP lan 1 phai bi vo hieu hoa</t>
+          <t>[SEC-07] Xin OTP lần 2 thì OTP lần 1 phải bị vô hiệu hóa</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>OTP cap lan 1 phai bi vo hieu hoa sau khi cap OTP lan 2; body co truong error</t>
+          <t>OTP cấp lần 1 phải bị vô hiệu hóa sau khi cấp OTP lần 2; body có trường error</t>
         </is>
       </c>
       <c r="N59" s="4" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>R1 - Ky vong 429 khong co can cu trong SRS (khong co yeu cau gioi han so lan goi). DA SUA: doi thanh dieu SEC-07 that su quy dinh - OTP phai duoc vo hieu hoa khi bi thay the: xin OTP lan 2 roi dung lai OTP lan 1.</t>
+          <t>R1 - Kỳ vọng 429 không có căn cứ trong SRS (không có yêu cầu giới hạn số lần gọi). ĐÃ SỬA: đổi thành điều SEC-07 thật sự quy định - OTP phải được vô hiệu hóa khi bị thay thế: xin OTP lần 2 rồi dùng lại OTP lần 1.</t>
         </is>
       </c>
       <c r="T59" s="4" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Response 200 cua forgot-password khop schema { message: string }</t>
+          <t>Response 200 của forgot-password khớp schema { message: string }</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="M60" s="5" t="inlineStr">
         <is>
-          <t>Content-Type application/json; body khop { message: string }; additionalProperties=false</t>
+          <t>Content-Type application/json; body khớp { message: string }; additionalProperties=false</t>
         </is>
       </c>
       <c r="N60" s="5" t="inlineStr">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="S60" s="5" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T60" s="5" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Response loi cua forgot-password khop schema { error: string }</t>
+          <t>Response lỗi của forgot-password khớp schema { error: string }</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>body khop { error: string }; chi co dung 1 truong</t>
+          <t>body khớp { error: string }; chỉ có đúng 1 trường</t>
         </is>
       </c>
       <c r="N61" s="5" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="S61" s="5" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T61" s="5" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Response 200 cua reset-password khop schema { message: string }</t>
+          <t>Response 200 của reset-password khớp schema { message: string }</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>Folder _setup da chay xong va da dat cac bien moi truong can thiet</t>
+          <t>Folder _setup đã chạy xong và đã đặt các biến môi trường cần thiết</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="S62" s="5" t="inlineStr">
         <is>
-          <t>R10 - Case dung bien Postman ({{...}}) nhung precondition chi ghi 'SUT da seed', khong noi bien do duoc dat o dau. Chay doc lap se that bai. DA SUA: ghi ro buoc _setup phai chay truoc.</t>
+          <t>R10 - Case dùng biến Postman ({{...}}) nhưng precondition chỉ ghi 'SUT da seed', không nói biến đó được đặt ở đâu. Chạy độc lập sẽ thất bại. ĐÃ SỬA: ghi rõ bước _setup phải chạy trước.</t>
         </is>
       </c>
       <c r="T62" s="5" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Response loi cua reset-password khop schema { error: string }</t>
+          <t>Response lỗi của reset-password khớp schema { error: string }</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="S63" s="5" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T63" s="5" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Response cua login khop schema { token: string, user: {...} } khong co password</t>
+          <t>Response của login khớp schema { token: string, user: {...} } không có password</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="M64" s="5" t="inlineStr">
         <is>
-          <t>body khop schema; body KHONG chua password</t>
+          <t>body khớp schema; body KHÔNG chứa password</t>
         </is>
       </c>
       <c r="N64" s="5" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="S64" s="5" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T64" s="5" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>Moi response loi deu phai la application/json chu khong phai HTML</t>
+          <t>Mọi response lỗi đều phải là application/json chứ không phải HTML</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
@@ -7792,7 +7792,7 @@
       </c>
       <c r="M65" s="5" t="inlineStr">
         <is>
-          <t>Content-Type application/json; body khong chua &lt;h1&gt;</t>
+          <t>Content-Type application/json; body không chứa &lt;h1&gt;</t>
         </is>
       </c>
       <c r="N65" s="5" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="S65" s="5" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T65" s="5" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Sau khi reset, mat khau CU phai het hieu luc va mat khau MOI phai dang nhap duoc</t>
+          <t>Sau khi reset, mật khẩu CŨ phải hết hiệu lực và mật khẩu MỚI phải đăng nhập được</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>Da chay xong chuoi: forgot-password -&gt; reset-password voi newPassword = NewApi1234!</t>
+          <t>Đã chạy xong chuỗi: forgot-password -&gt; reset-password với newPassword = NewApi1234!</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>login bang mat khau CU tra 401; ngay sau do login bang mat khau MOI tra 200 kem token</t>
+          <t>login bằng mật khẩu CŨ trả 401; ngay sau đó login bằng mật khẩu MỚI trả 200 kèm token</t>
         </is>
       </c>
       <c r="N66" s="3" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="S66" s="3" t="inlineStr">
         <is>
-          <t>Case do sinh vien tu viet sau khi doc ma nguon SUT; khong qua bo sinh tu dong.</t>
+          <t>Case do sinh viên tự viết sau khi đọc mã nguồn SUT; không qua bộ sinh tự động.</t>
         </is>
       </c>
       <c r="T66" s="3" t="inlineStr">
@@ -7945,7 +7945,7 @@
       </c>
       <c r="V66" s="3" t="inlineStr">
         <is>
-          <t>API - Bo sinh chi kiem RESPONSE cua reset-password ('Password reset successfully') roi dung lai. Nhung cau tra loi do khong chung minh mat khau da thuc su doi: SUT co the tra 200 ma khong ghi gi (chinh la kieu loi C-07/C-08 o API-3). Chi mot chuoi 3 request - reset, login mat khau cu, login mat khau moi - moi chung minh duoc. Bo sinh lam viec tren tung case doc lap nen khong the tu dung chuoi nay.</t>
+          <t>API - Bộ sinh chỉ kiểm RESPONSE của reset-password ('Password reset successfully') rồi dừng lại. Nhưng câu trả lời đó không chứng minh mật khẩu đã thực sự đổi: SUT có thể trả 200 mà không ghi gì (chính là kiểu lỗi C-07/C-08 ở API-3). Chỉ một chuỗi 3 request - reset, login mật khẩu cũ, login mật khẩu mới - mới chứng minh được. Bộ sinh làm việc trên từng case độc lập nên không thể tự dựng chuỗi này.</t>
         </is>
       </c>
     </row>
@@ -7977,7 +7977,7 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>[-] Dat lai mat khau thanh cong nhung tai khoan van bi khoa</t>
+          <t>[-] Đặt lại mật khẩu thành công nhưng tài khoản vẫn bị khóa</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
@@ -7992,7 +7992,7 @@
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>Tai khoan da bi khoa do dang nhap sai; sau do da reset mat khau thanh cong bang OTP</t>
+          <t>Tài khoản đã bị khóa do đăng nhập sai; sau đó đã reset mật khẩu thành công bằng OTP</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
@@ -8012,7 +8012,7 @@
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>dang nhap thanh cong bang mat khau moi; login_attempts phai ve 0 va locked_until phai duoc xoa sau khi reset</t>
+          <t>đăng nhập thành công bằng mật khẩu mới; login_attempts phải về 0 và locked_until phải được xóa sau khi reset</t>
         </is>
       </c>
       <c r="N67" s="4" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>Case do sinh vien tu viet sau khi doc ma nguon SUT; khong qua bo sinh tu dong.</t>
+          <t>Case do sinh viên tự viết sau khi đọc mã nguồn SUT; không qua bộ sinh tự động.</t>
         </is>
       </c>
       <c r="T67" s="4" t="inlineStr">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="V67" s="4" t="inlineStr">
         <is>
-          <t>API - Bug nam o CHO GIAO NHAU giua hai chuc nang: FR-02 (khoa tai khoan) va FR-03 (dat lai mat khau). Cau lenh UPDATE trong reset-password chi dat lai password va reset_token, khong dong toi login_attempts va locked_until. Bo sinh chi doc dac ta cua FR-03 nen khong the biet FR-02 co de lai trang thai gi. Can 5 request lien tiep (2 lan login sai, forgot, reset, login) moi tai hien duoc.</t>
+          <t>API - Bug nằm ở CHỖ GIAO NHAU giữa hai chức năng: FR-02 (khóa tài khoản) và FR-03 (đặt lại mật khẩu). Câu lệnh UPDATE trong reset-password chỉ đặt lại password và reset_token, không động tới login_attempts và locked_until. Bộ sinh chỉ đọc đặc tả của FR-03 nên không thể biết FR-02 có để lại trạng thái gì. Cần 5 request liên tiếp (2 lần login sai, forgot, reset, login) mới tái hiện được.</t>
         </is>
       </c>
     </row>
@@ -8124,7 +8124,7 @@
       </c>
       <c r="M68" s="4" t="inlineStr">
         <is>
-          <t>body KHONG duoc chua truong password; KHONG duoc chua truong reset_token; neu password xuat hien dung nguyen van chuoi da gui khi dang ky thi da chung minh vi pham SEC-01</t>
+          <t>body KHÔNG được chứa trường password; KHÔNG được chứa trường reset_token; nếu password xuất hiện đúng nguyên văn chuỗi đã gửi khi đăng ký thì đã chứng minh vi phạm SEC-01</t>
         </is>
       </c>
       <c r="N68" s="4" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>Case do sinh vien tu viet sau khi doc ma nguon SUT; khong qua bo sinh tu dong.</t>
+          <t>Case do sinh viên tự viết sau khi đọc mã nguồn SUT; không qua bộ sinh tự động.</t>
         </is>
       </c>
       <c r="T68" s="4" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="V68" s="4" t="inlineStr">
         <is>
-          <t>PROMPT - Prompt khoanh vung API-1 vao dung hai endpoint forgot-password va reset-password. Nhung noi ro ri nghiem trong nhat lai la GET /api/users/me: no lam `SELECT * FROM users` roi tra thang ca ban ghi, ke ca cot reset_token dang con hieu luc. Ke tan cong doc duoc OTP cua chinh minh la vo hai, nhung no chung minh cot nay chua bao gio duoc coi la bi mat. Bo sinh khong duoc phep buoc ra ngoai pham vi prompt.</t>
+          <t>PROMPT - Prompt khoanh vùng API-1 vào đúng hai endpoint forgot-password và reset-password. Nhưng nơi rò rỉ nghiêm trọng nhất lại là GET /api/users/me: nó làm `SELECT * FROM users` rồi trả thẳng cả bản ghi, kể cả cột reset_token đang còn hiệu lực. Kẻ tấn công đọc được OTP của chính mình là vô hại, nhưng nó chứng minh cột này chưa bao giờ được coi là bí mật. Bộ sinh không được phép bước ra ngoài phạm vi prompt.</t>
         </is>
       </c>
     </row>
@@ -8201,7 +8201,7 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>[-] Tai khoan bi khoa ngay sau HAI lan dang nhap sai, trong khi SRS quy dinh ba lan</t>
+          <t>[-] Tài khoản bị khóa ngay sau HAI lần đăng nhập sai, trong khi SRS quy định ba lần</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>Tai khoan api.victim vua duoc seed lai, login_attempts = 0. Da goi login sai DUNG HAI lan truoc do</t>
+          <t>Tài khoản api.victim vừa được seed lại, login_attempts = 0. Đã gọi login sai ĐÚNG HAI lần trước đó</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>sau DUNG hai lan sai, dang nhap bang mat khau DUNG van phai thanh cong (SRS FR-02: chi khoa tu lan sai thu ba)</t>
+          <t>sau ĐÚNG hai lần sai, đăng nhập bằng mật khẩu ĐÚNG vẫn phải thành công (SRS FR-02: chỉ khóa từ lần sai thứ ba)</t>
         </is>
       </c>
       <c r="N69" s="4" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>Case do sinh vien tu viet sau khi doc ma nguon SUT; khong qua bo sinh tu dong.</t>
+          <t>Case do sinh viên tự viết sau khi đọc mã nguồn SUT; không qua bộ sinh tự động.</t>
         </is>
       </c>
       <c r="T69" s="4" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="V69" s="4" t="inlineStr">
         <is>
-          <t>MODEL - SRS viet 'sai tu 3 lan tro len thi khoa', va bo sinh sinh dung case do: sai 3 lan roi kiem da khoa chua. Case do PASS, vi sai 3 lan thi qua nhien la khoa. Bug nam o phia con lai cua bien: code cong +2 moi lan sai nen mo khoa ngay o lan thu HAI. Muon thay phai kiem canh 'chua duoc khoa' chu khong phai canh 'da bi khoa' - AI mac dinh viet case khang dinh dieu dac ta noi, chu khong viet case phu dinh dieu dac ta khong noi.</t>
+          <t>MODEL - SRS viết 'sai từ 3 lần trở lên thì khóa', và bộ sinh sinh đúng case đó: sai 3 lần rồi kiểm đã khóa chưa. Case đó PASS, vì sai 3 lần thì quá nhiên là khóa. Bug nằm ở phía còn lại của biên: code cộng +2 mỗi lần sai nên mở khóa ngay ở lần thứ HAI. Muốn thấy phải kiểm cạnh 'chưa được khóa' chứ không phải cạnh 'đã bị khóa' - AI mặc định viết case khẳng định điều đặc tả nói, chứ không viết case phủ định điều đặc tả không nói.</t>
         </is>
       </c>
     </row>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>[SEC-03] User thuong doc duoc toan bo bang users qua GET /api/admin/users</t>
+          <t>[SEC-03] User thường đọc được toàn bộ bảng users qua GET /api/admin/users</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
-          <t>Da login bang tai khoan thuong api.victim, co {{token_user}}</t>
+          <t>Đã login bằng tài khoản thường api.victim, có {{token_user}}</t>
         </is>
       </c>
       <c r="J70" s="4" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="M70" s="4" t="inlineStr">
         <is>
-          <t>token hop le nhung role = 'user' thi phai bi tu choi 403; khong duoc tra ve danh sach email cua nguoi khac</t>
+          <t>token hợp lệ nhưng role = 'user' thì phải bị từ chối 403; không được trả về danh sách email của người khác</t>
         </is>
       </c>
       <c r="N70" s="4" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>Case do sinh vien tu viet sau khi doc ma nguon SUT; khong qua bo sinh tu dong.</t>
+          <t>Case do sinh viên tự viết sau khi đọc mã nguồn SUT; không qua bộ sinh tự động.</t>
         </is>
       </c>
       <c r="T70" s="4" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="V70" s="4" t="inlineStr">
         <is>
-          <t>PROMPT - API-1 khong co endpoint admin nao nen bo sinh khong sinh case SEC-03. Nhung luong quen mat khau van co the bi khai thac qua duong nay: GET /api/admin/users tra ve ca login_attempts va locked_until cua moi nguoi, cho phep do xem tai khoan nao dang bi khoa. Do phu SEC-03 cua API-1 truoc do la 0 - day la case lam day khoang trong do bang mot kich ban co that.</t>
+          <t>PROMPT - API-1 không có endpoint admin nào nên bộ sinh không sinh case SEC-03. Nhưng luồng quên mật khẩu vẫn có thể bị khai thác qua đường này: GET /api/admin/users trả về cả login_attempts và locked_until của mọi người, cho phép dò xem tài khoản nào đang bị khóa. Độ phủ SEC-03 của API-1 trước đó là 0 - đây là case làm đầy khoảng trống đó bằng một kịch bản có thật.</t>
         </is>
       </c>
     </row>
@@ -8425,7 +8425,7 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>[SEC-07] OTP cua nguoi nay dung duoc cho email cua nguoi kia neu trung gia tri</t>
+          <t>[SEC-07] OTP của người này dùng được cho email của người kia nếu trùng giá trị</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>Ca hai tai khoan victim va attacker deu da goi forgot-password. Ghi lai OTP cua attacker</t>
+          <t>Cả hai tài khoản victim và attacker đều đã gọi forgot-password. Ghi lại OTP của attacker</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
@@ -8460,7 +8460,7 @@
       </c>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>OTP cua tai khoan khac phai bi tu choi; mat khau cua victim KHONG duoc doi; voi khong gian chi 9000 gia tri, xac suat hai OTP trung nhau la dang ke nen dieu kien AND email + token la khong du</t>
+          <t>OTP của tài khoản khác phải bị từ chối; mật khẩu của victim KHÔNG được đổi; với không gian chỉ 9000 giá trị, xác suất hai OTP trùng nhau là đáng kể nên điều kiện AND email + token là không đủ</t>
         </is>
       </c>
       <c r="N71" s="4" t="inlineStr">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>Case do sinh vien tu viet sau khi doc ma nguon SUT; khong qua bo sinh tu dong.</t>
+          <t>Case do sinh viên tự viết sau khi đọc mã nguồn SUT; không qua bộ sinh tự động.</t>
         </is>
       </c>
       <c r="T71" s="4" t="inlineStr">
@@ -8505,7 +8505,7 @@
       </c>
       <c r="V71" s="4" t="inlineStr">
         <is>
-          <t>SPECGAP - Dac ta chi noi 'OTP chi hop le cho email da yeu cau', va cau UPDATE cua SUT co ca hai dieu kien WHERE email = ? AND reset_token = ? nen thoat nhin la dung. Cai dac ta KHONG noi la khong gian OTP phai du lon de hai nguoi khong trung ma. Voi 4 chu so, chi can 100 nguoi cung dang cho reset la kha nang trung vuot 40%. AI khong co cau nao trong dac ta de bam vao nen khong sinh case nay.</t>
+          <t>SPECGAP - Đặc tả chỉ nói 'OTP chỉ hợp lệ cho email đã yêu cầu', và câu UPDATE của SUT có cả hai điều kiện WHERE email = ? AND reset_token = ? nên thoạt nhìn là đúng. Cái đặc tả KHÔNG nói là không gian OTP phải đủ lớn để hai người không trùng mã. Với 4 chữ số, chỉ cần 100 người cùng đang chờ reset là khả năng trùng vượt 40%. AI không có câu nào trong đặc tả để bám vào nên không sinh case này.</t>
         </is>
       </c>
     </row>
@@ -8688,7 +8688,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>POST /api/checkout | total_amount = 200000 (tong tien khop voi gio hang)</t>
+          <t>POST /api/checkout | total_amount = 200000 (tổng tiền khớp với giỏ hàng)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Da login, co {{token_user}}, gio hang co 1 san pham</t>
+          <t>Đã login, có {{token_user}}, giỏ hàng có 1 sản phẩm</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>body co orderId; total_amount trong DB = tong tinh tu server</t>
+          <t>body có orderId; total_amount trong DB = tổng tính từ server</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>POST /api/checkout | total_amount = 1 (client gui tong tien 1 dong - server phai tu tinh lai)</t>
+          <t>POST /api/checkout | total_amount = 1 (client gửi tổng tiền 1 đồng - server phải tự tính lại)</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Da login, co {{token_user}}, gio hang co 1 san pham</t>
+          <t>Đã login, có {{token_user}}, giỏ hàng có 1 sản phẩm</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>don hang KHONG duoc tao voi gia 1; GET /api/orders/:id phai tra dung gia that</t>
+          <t>đơn hàng KHÔNG được tạo với giá 1; GET /api/orders/:id phải trả đúng giá thật</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
@@ -8919,7 +8919,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Da login, co {{token_user}}, gio hang co 1 san pham</t>
+          <t>Đã login, có {{token_user}}, giỏ hàng có 1 sản phẩm</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8969,7 +8969,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Da login, co {{token_user}}, gio hang co 1 san pham</t>
+          <t>Đã login, có {{token_user}}, giỏ hàng có 1 sản phẩm</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9047,7 +9047,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>POST /api/checkout | total_amount = 200000 (tong tien sai kieu (string))</t>
+          <t>POST /api/checkout | total_amount = 200000 (tổng tiền sai kiểu (string))</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9135,7 +9135,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Da login, co {{token_user}}, gio hang co 1 san pham</t>
+          <t>Đã login, có {{token_user}}, giỏ hàng có 1 sản phẩm</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9185,7 +9185,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>POST /api/checkout | total_amount = &lt;thieu key&gt; (thieu total_amount)</t>
+          <t>POST /api/checkout | total_amount = &lt;thieu key&gt; (thiếu total_amount)</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9243,7 +9243,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Da login, co {{token_user}}, gio hang co 1 san pham</t>
+          <t>Đã login, có {{token_user}}, giỏ hàng có 1 sản phẩm</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9293,7 +9293,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Da login, co {{token_user}}, gio hang co 1 san pham</t>
+          <t>Đã login, có {{token_user}}, giỏ hàng có 1 sản phẩm</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Da login, co {{token_user}}, gio hang co 1 san pham</t>
+          <t>Đã login, có {{token_user}}, giỏ hàng có 1 sản phẩm</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
@@ -9567,7 +9567,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Da login, co {{token_user}}, gio hang co 1 san pham</t>
+          <t>Đã login, có {{token_user}}, giỏ hàng có 1 sản phẩm</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -9660,7 +9660,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>POST /api/checkout | items = [] (gio hang rong)</t>
+          <t>POST /api/checkout | items = [] (giỏ hàng rỗng)</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9675,7 +9675,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Da login, co {{token_user}}, gio hang co 1 san pham</t>
+          <t>Đã login, có {{token_user}}, giỏ hàng có 1 sản phẩm</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>khong duoc tao don hang rong</t>
+          <t>không được tạo đơn hàng rỗng</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -9768,7 +9768,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>POST /api/checkout | items = &lt;thieu key&gt; (thieu items - server hien bo qua hoan toan)</t>
+          <t>POST /api/checkout | items = &lt;thieu key&gt; (thiếu items - server hiện bỏ qua hoàn toàn)</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9783,7 +9783,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Da login, co {{token_user}}, gio hang co 1 san pham</t>
+          <t>Đã login, có {{token_user}}, giỏ hàng có 1 sản phẩm</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>POST /api/checkout | items = [{"product_id":1,"quantity":0}] (BVA - so luong 0)</t>
+          <t>POST /api/checkout | items = [{"product_id":1,"quantity":0}] (BVA - số lượng 0)</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Da login, co {{token_user}}, gio hang co 1 san pham</t>
+          <t>Đã login, có {{token_user}}, giỏ hàng có 1 sản phẩm</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>POST /api/checkout | items = [{"product_id":1,"quantity":-5}] (so luong am (co the sinh tien am))</t>
+          <t>POST /api/checkout | items = [{"product_id":1,"quantity":-5}] (số lượng âm (có thể sinh tiền âm))</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9999,7 +9999,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Da login, co {{token_user}}, gio hang co 1 san pham</t>
+          <t>Đã login, có {{token_user}}, giỏ hàng có 1 sản phẩm</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10019,7 +10019,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -10092,7 +10092,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>POST /api/checkout | items = [{"product_id":1,"quantity":1}] (BVA - so luong 1 (bien duoi hop le))</t>
+          <t>POST /api/checkout | items = [{"product_id":1,"quantity":1}] (BVA - số lượng 1 (biên dưới hợp lệ))</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10107,7 +10107,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Da login, co {{token_user}}, gio hang co 1 san pham</t>
+          <t>Đã login, có {{token_user}}, giỏ hàng có 1 sản phẩm</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10127,7 +10127,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; khop schema thanh cong; VA doc lai tai nguyen de xac nhan gia tri luu dung bang gia tri da gui</t>
+          <t>body là JSON; khớp schema thành công; VA doc lai tai nguyen de xac nhan gia tri luu dung bang gia tri da gui</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>R8 - Case thanh cong nhung chi kiem 'khop schema'. Thieu khang dinh gia tri that su duoc luu dung. DA SUA: bo sung buoc doc lai tai nguyen va so khop gia tri vua gui.</t>
+          <t>R8 - Case thành công nhưng chỉ kiểm 'khớp schema'. Thiếu khẳng định giá trị thật sự được lưu đúng. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên và so khớp giá trị vừa gửi.</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
@@ -10200,7 +10200,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>POST /api/checkout | items = [{"product_id":999999,"quantity":1}] (san pham khong ton tai)</t>
+          <t>POST /api/checkout | items = [{"product_id":999999,"quantity":1}] (sản phẩm không tồn tại)</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Da login, co {{token_user}}, gio hang co 1 san pham</t>
+          <t>Đã login, có {{token_user}}, giỏ hàng có 1 sản phẩm</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10235,7 +10235,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10265,7 +10265,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Da login, co {{token_user}}, gio hang co 1 san pham</t>
+          <t>Đã login, có {{token_user}}, giỏ hàng có 1 sản phẩm</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -10416,7 +10416,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>POST /api/checkout | items = khong-phai-array (items sai kieu)</t>
+          <t>POST /api/checkout | items = khong-phai-array (items sai kiểu)</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Da login, co {{token_user}}, gio hang co 1 san pham</t>
+          <t>Đã login, có {{token_user}}, giỏ hàng có 1 sản phẩm</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10451,7 +10451,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>POST /api/checkout | shipping_address = 123 Nguyen Van Cu, Q5, TP.HCM (dia chi hop le)</t>
+          <t>POST /api/checkout | shipping_address = 123 Nguyen Van Cu, Q5, TP.HCM (địa chỉ hợp lệ)</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10539,7 +10539,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Da login, co {{token_user}}, gio hang co 1 san pham</t>
+          <t>Đã login, có {{token_user}}, giỏ hàng có 1 sản phẩm</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10559,7 +10559,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; khop schema thanh cong; VA doc lai tai nguyen de xac nhan gia tri luu dung bang gia tri da gui</t>
+          <t>body là JSON; khớp schema thành công; VA doc lai tai nguyen de xac nhan gia tri luu dung bang gia tri da gui</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10589,7 +10589,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>R8 - Case thanh cong nhung chi kiem 'khop schema'. Thieu khang dinh gia tri that su duoc luu dung. DA SUA: bo sung buoc doc lai tai nguyen va so khop gia tri vua gui.</t>
+          <t>R8 - Case thành công nhưng chỉ kiểm 'khớp schema'. Thiếu khẳng định giá trị thật sự được lưu đúng. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên và so khớp giá trị vừa gửi.</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
@@ -10632,7 +10632,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>POST /api/checkout | shipping_address =  (dia chi rong)</t>
+          <t>POST /api/checkout | shipping_address =  (địa chỉ rỗng)</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Da login, co {{token_user}}, gio hang co 1 san pham</t>
+          <t>Đã login, có {{token_user}}, giỏ hàng có 1 sản phẩm</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10667,7 +10667,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>POST /api/checkout | shipping_address = - (dia chi null - hien van tao duoc don)</t>
+          <t>POST /api/checkout | shipping_address = - (địa chỉ null - hiện vẫn tạo được đơn)</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10755,7 +10755,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Da login, co {{token_user}}, gio hang co 1 san pham</t>
+          <t>Đã login, có {{token_user}}, giỏ hàng có 1 sản phẩm</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
@@ -10848,7 +10848,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>POST /api/checkout | shipping_address = &lt;thieu key&gt; (thieu dia chi)</t>
+          <t>POST /api/checkout | shipping_address = &lt;thieu key&gt; (thiếu địa chỉ)</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Da login, co {{token_user}}, gio hang co 1 san pham</t>
+          <t>Đã login, có {{token_user}}, giỏ hàng có 1 sản phẩm</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10883,7 +10883,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -10971,7 +10971,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Da login, co {{token_user}}, gio hang co 1 san pham</t>
+          <t>Đã login, có {{token_user}}, giỏ hàng có 1 sản phẩm</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>R3 - Gan sai ma SEC (SEC-06 -&gt; SEC-04). Payload &lt;script&gt; trong shipping_address -&gt; SEC-04. SRS FR-18 con noi ro dia chi giao hang phai hien thi an toan.</t>
+          <t>R3 - Gan sai ma SEC (SEC-06 -&gt; SEC-04). Payload &lt;script&gt; trong shipping_address -&gt; SEC-04. SRS FR-18 còn nói rõ địa chỉ giao hàng phải hiển thị an toàn.</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>POST /api/checkout | shipping_address = A123456789A123456789A123456789A123456789 (BVA - dia chi vuot 255 ky tu)</t>
+          <t>POST /api/checkout | shipping_address = A123456789A123456789A123456789A123456789 (BVA - địa chỉ vượt 255 ký tự)</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Da login, co {{token_user}}, gio hang co 1 san pham</t>
+          <t>Đã login, có {{token_user}}, giỏ hàng có 1 sản phẩm</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11129,7 +11129,7 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>POST /api/apply-coupon | code = SAVE10 (Decision table T1 - ma % hop le, du dieu kien)</t>
+          <t>POST /api/apply-coupon | code = SAVE10 (Decision table T1 - mã % hợp lệ, đủ điều kiện)</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11187,7 +11187,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 luot), EXPIRED (percent 20, min 100000, het han 2020-01-01) da co san tu database.js</t>
+          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 lượt), EXPIRED (percent 20, min 100000, hết hạn 2020-01-01) đã có sẵn từ database.js</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11207,7 +11207,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>discount_amount = 50000 (10% cua 500000) theo cong thuc SRS FR-09</t>
+          <t>discount_amount = 50000 (10% của 500000) theo công thức SRS FR-09</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11237,7 +11237,7 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>POST /api/apply-coupon | code = BIGBUY (Decision table T2 - ma so tien co dinh)</t>
+          <t>POST /api/apply-coupon | code = BIGBUY (Decision table T2 - mã số tiền cố định)</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11295,7 +11295,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 luot), EXPIRED (percent 20, min 100000, het han 2020-01-01) da co san tu database.js</t>
+          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 lượt), EXPIRED (percent 20, min 100000, hết hạn 2020-01-01) đã có sẵn từ database.js</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11345,7 +11345,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -11388,7 +11388,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>POST /api/apply-coupon | code = EXPIRED (Decision table T3 - ma het han)</t>
+          <t>POST /api/apply-coupon | code = EXPIRED (Decision table T3 - mã hết hạn)</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 luot), EXPIRED (percent 20, min 100000, het han 2020-01-01) da co san tu database.js</t>
+          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 lượt), EXPIRED (percent 20, min 100000, hết hạn 2020-01-01) đã có sẵn từ database.js</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11423,7 +11423,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>POST /api/apply-coupon | code = VIP100 (Decision table T4 - ma fixed con luot dung (max 2 luot/user). Khong co coupon is_active=0 nao duoc seed nen dong T4 goc (ma bi vo hieu hoa) khong kiem duoc qua API - xem report/01_api_selection.md)</t>
+          <t>POST /api/apply-coupon | code = VIP100 (Decision table T4 - mã fixed còn lượt dùng (max 2 lượt/user). Không có coupon is_active=0 nào được seed nên dòng T4 gốc (mã bị vô hiệu hóa) không kiểm được qua API - xem report/01_api_selection.md)</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11511,7 +11511,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 luot), EXPIRED (percent 20, min 100000, het han 2020-01-01) da co san tu database.js</t>
+          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 lượt), EXPIRED (percent 20, min 100000, hết hạn 2020-01-01) đã có sẵn từ database.js</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
@@ -11604,7 +11604,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>POST /api/apply-coupon | code = KHONGCOMA23127060 (Decision table T5 - ma khong ton tai)</t>
+          <t>POST /api/apply-coupon | code = KHONGCOMA23127060 (Decision table T5 - mã không tồn tại)</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11619,7 +11619,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 luot), EXPIRED (percent 20, min 100000, het han 2020-01-01) da co san tu database.js</t>
+          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 lượt), EXPIRED (percent 20, min 100000, hết hạn 2020-01-01) đã có sẵn từ database.js</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11639,7 +11639,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>POST /api/apply-coupon | code =  (ma rong)</t>
+          <t>POST /api/apply-coupon | code =  (mã rỗng)</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 luot), EXPIRED (percent 20, min 100000, het han 2020-01-01) da co san tu database.js</t>
+          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 lượt), EXPIRED (percent 20, min 100000, hết hạn 2020-01-01) đã có sẵn từ database.js</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11747,7 +11747,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11777,7 +11777,7 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
@@ -11820,7 +11820,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>POST /api/apply-coupon | code = &lt;thieu key&gt; (thieu code)</t>
+          <t>POST /api/apply-coupon | code = &lt;thieu key&gt; (thiếu code)</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11835,7 +11835,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 luot), EXPIRED (percent 20, min 100000, het han 2020-01-01) da co san tu database.js</t>
+          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 lượt), EXPIRED (percent 20, min 100000, hết hạn 2020-01-01) đã có sẵn từ database.js</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11855,7 +11855,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11885,7 +11885,7 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>POST /api/apply-coupon | code = ' OR '1'='1 (SQLi trong ma giam gia)</t>
+          <t>POST /api/apply-coupon | code = ' OR '1'='1 (SQLi trong mã giảm giá)</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 luot), EXPIRED (percent 20, min 100000, het han 2020-01-01) da co san tu database.js</t>
+          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 lượt), EXPIRED (percent 20, min 100000, hết hạn 2020-01-01) đã có sẵn từ database.js</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11963,7 +11963,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>POST /api/apply-coupon | code = perc10 (ma viet thuong - hanh vi phai nhat quan voi spec)</t>
+          <t>POST /api/apply-coupon | code = perc10 (mã viết thường - hành vi phải nhất quán với spec)</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 luot), EXPIRED (percent 20, min 100000, het han 2020-01-01) da co san tu database.js</t>
+          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 lượt), EXPIRED (percent 20, min 100000, hết hạn 2020-01-01) đã có sẵn từ database.js</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12071,7 +12071,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; khop schema thanh cong; VA doc lai tai nguyen de xac nhan gia tri luu dung bang gia tri da gui</t>
+          <t>body là JSON; khớp schema thành công; VA doc lai tai nguyen de xac nhan gia tri luu dung bang gia tri da gui</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12101,7 +12101,7 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>R8 - Case thanh cong nhung chi kiem 'khop schema'. Thieu khang dinh gia tri that su duoc luu dung. DA SUA: bo sung buoc doc lai tai nguyen va so khop gia tri vua gui.</t>
+          <t>R8 - Case thành công nhưng chỉ kiểm 'khớp schema'. Thiếu khẳng định giá trị thật sự được lưu đúng. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên và so khớp giá trị vừa gửi.</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
@@ -12144,7 +12144,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>POST /api/apply-coupon | total_amount = 299999 (BVA - duoi min_order_amount 300000 cua SAVE10 dung 1 dong)</t>
+          <t>POST /api/apply-coupon | total_amount = 299999 (BVA - dưới min_order_amount 300000 của SAVE10 đúng 1 đồng)</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 luot), EXPIRED (percent 20, min 100000, het han 2020-01-01) da co san tu database.js</t>
+          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 lượt), EXPIRED (percent 20, min 100000, hết hạn 2020-01-01) đã có sẵn từ database.js</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12209,7 +12209,7 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>POST /api/apply-coupon | total_amount = 300000 (BVA - BANG dung min_order_amount 300000 (loi bien &gt; thay vi &gt;=))</t>
+          <t>POST /api/apply-coupon | total_amount = 300000 (BVA - BẰNG đúng min_order_amount 300000 (lỗi biên &gt; thay vì &gt;=))</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12267,7 +12267,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 luot), EXPIRED (percent 20, min 100000, het han 2020-01-01) da co san tu database.js</t>
+          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 lượt), EXPIRED (percent 20, min 100000, hết hạn 2020-01-01) đã có sẵn từ database.js</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12287,7 +12287,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>phai duoc ap ma vi dieu kien la &gt;= min_order_amount</t>
+          <t>phải được áp mã vì điều kiện là &gt;= min_order_amount</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>POST /api/apply-coupon | total_amount = 300001 (BVA - tren min_order_amount 300000 dung 1 dong)</t>
+          <t>POST /api/apply-coupon | total_amount = 300001 (BVA - trên min_order_amount 300000 đúng 1 đồng)</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12375,7 +12375,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 luot), EXPIRED (percent 20, min 100000, het han 2020-01-01) da co san tu database.js</t>
+          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 lượt), EXPIRED (percent 20, min 100000, hết hạn 2020-01-01) đã có sẵn từ database.js</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12395,7 +12395,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; khop schema thanh cong; VA doc lai tai nguyen de xac nhan gia tri luu dung bang gia tri da gui</t>
+          <t>body là JSON; khớp schema thành công; VA doc lai tai nguyen de xac nhan gia tri luu dung bang gia tri da gui</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12425,7 +12425,7 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>R8 - Case thanh cong nhung chi kiem 'khop schema'. Thieu khang dinh gia tri that su duoc luu dung. DA SUA: bo sung buoc doc lai tai nguyen va so khop gia tri vua gui.</t>
+          <t>R8 - Case thành công nhưng chỉ kiểm 'khớp schema'. Thiếu khẳng định giá trị thật sự được lưu đúng. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên và so khớp giá trị vừa gửi.</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
@@ -12483,7 +12483,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 luot), EXPIRED (percent 20, min 100000, het han 2020-01-01) da co san tu database.js</t>
+          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 lượt), EXPIRED (percent 20, min 100000, hết hạn 2020-01-01) đã có sẵn từ database.js</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12503,7 +12503,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12533,7 +12533,7 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
@@ -12576,7 +12576,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>POST /api/apply-coupon | total_amount = 10000 (don 10k nho hon so tien giam - final_amount khong duoc am)</t>
+          <t>POST /api/apply-coupon | total_amount = 10000 (đơn 10k nhỏ hơn số tiền giảm - final_amount không được âm)</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -12591,7 +12591,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 luot), EXPIRED (percent 20, min 100000, het han 2020-01-01) da co san tu database.js</t>
+          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 lượt), EXPIRED (percent 20, min 100000, hết hạn 2020-01-01) đã có sẵn từ database.js</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -12611,7 +12611,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>POST /api/apply-coupon | user_id = {{userId}} (user_id cua chinh minh)</t>
+          <t>POST /api/apply-coupon | user_id = {{userId}} (user_id của chính mình)</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -12699,7 +12699,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 luot), EXPIRED (percent 20, min 100000, het han 2020-01-01) da co san tu database.js</t>
+          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 lượt), EXPIRED (percent 20, min 100000, hết hạn 2020-01-01) đã có sẵn từ database.js</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -12719,7 +12719,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; khop schema thanh cong; VA doc lai tai nguyen de xac nhan gia tri luu dung bang gia tri da gui</t>
+          <t>body là JSON; khớp schema thành công; VA doc lai tai nguyen de xac nhan gia tri luu dung bang gia tri da gui</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>R8 - Case thanh cong nhung chi kiem 'khop schema'. Thieu khang dinh gia tri that su duoc luu dung. DA SUA: bo sung buoc doc lai tai nguyen va so khop gia tri vua gui.</t>
+          <t>R8 - Case thành công nhưng chỉ kiểm 'khớp schema'. Thiếu khẳng định giá trị thật sự được lưu đúng. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên và so khớp giá trị vừa gửi.</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
@@ -12792,7 +12792,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>POST /api/apply-coupon | user_id = 99999 (user_id cua nguoi khac - server phai lay tu JWT)</t>
+          <t>POST /api/apply-coupon | user_id = 99999 (user_id của người khác - server phải lấy từ JWT)</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -12807,7 +12807,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 luot), EXPIRED (percent 20, min 100000, het han 2020-01-01) da co san tu database.js</t>
+          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 lượt), EXPIRED (percent 20, min 100000, hết hạn 2020-01-01) đã có sẵn từ database.js</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -12827,7 +12827,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -12857,7 +12857,7 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>R3 - Gan sai ma SEC (SEC-04 -&gt; SEC-02). Lay user_id tu body thay vi tu JWT la vi pham SEC-02 (API bao mat phai dua tren token hop le), khong phai SEC-04.</t>
+          <t>R3 - Gan sai ma SEC (SEC-04 -&gt; SEC-02). Lấy user_id từ body thay vì từ JWT là vi phạm SEC-02 (API bảo mật phải dựa trên token hợp lệ), không phải SEC-04.</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>POST /api/apply-coupon | user_id = &lt;thieu key&gt; (thieu user_id - bypass kiem tra han muc su dung)</t>
+          <t>POST /api/apply-coupon | user_id = &lt;thieu key&gt; (thiếu user_id - bypass kiểm tra hạn mức sử dụng)</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -12915,7 +12915,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 luot), EXPIRED (percent 20, min 100000, het han 2020-01-01) da co san tu database.js</t>
+          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 lượt), EXPIRED (percent 20, min 100000, hết hạn 2020-01-01) đã có sẵn từ database.js</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -12965,7 +12965,7 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
@@ -13023,7 +13023,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 luot), EXPIRED (percent 20, min 100000, het han 2020-01-01) da co san tu database.js</t>
+          <t>Coupon SAVE10 (percent 10, min 300000), BIGBUY (fixed 50000, min 500000), VIP100 (fixed 100000, min 300000, max 2 lượt), EXPIRED (percent 20, min 100000, hết hạn 2020-01-01) đã có sẵn từ database.js</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -13043,7 +13043,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -13073,7 +13073,7 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
@@ -13116,7 +13116,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai pending -&gt; confirmed (hop le)</t>
+          <t>Chuyển trạng thái pending -&gt; confirmed (hợp lệ)</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -13131,7 +13131,7 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doi tuong dang o trang thai pending. </t>
+          <t xml:space="preserve">Đối tượng đang ở trạng thái pending. </t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -13151,7 +13151,7 @@
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>trang thai sau khi goi = confirmed</t>
+          <t>trạng thái sau khi gọi = confirmed</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
@@ -13181,7 +13181,7 @@
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai confirmed -&gt; shipping (hop le)</t>
+          <t>Chuyển trạng thái confirmed -&gt; shipping (hợp lệ)</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -13239,7 +13239,7 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doi tuong dang o trang thai confirmed. </t>
+          <t xml:space="preserve">Đối tượng đang ở trạng thái confirmed. </t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -13259,7 +13259,7 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>trang thai sau khi goi = shipping</t>
+          <t>trạng thái sau khi gọi = shipping</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -13289,7 +13289,7 @@
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
@@ -13332,7 +13332,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai shipping -&gt; delivered (hop le)</t>
+          <t>Chuyển trạng thái shipping -&gt; delivered (hợp lệ)</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -13347,7 +13347,7 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doi tuong dang o trang thai shipping. </t>
+          <t xml:space="preserve">Đối tượng đang ở trạng thái shipping. </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -13367,7 +13367,7 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>trang thai sau khi goi = delivered</t>
+          <t>trạng thái sau khi gọi = delivered</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
@@ -13397,7 +13397,7 @@
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
@@ -13440,7 +13440,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai pending -&gt; canceled (hop le)</t>
+          <t>Chuyển trạng thái pending -&gt; canceled (hợp lệ)</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -13455,7 +13455,7 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doi tuong dang o trang thai pending. </t>
+          <t xml:space="preserve">Đối tượng đang ở trạng thái pending. </t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>trang thai sau khi goi = canceled</t>
+          <t>trạng thái sau khi gọi = canceled</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
@@ -13505,7 +13505,7 @@
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
@@ -13548,7 +13548,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai confirmed -&gt; canceled (hop le)</t>
+          <t>Chuyển trạng thái confirmed -&gt; canceled (hợp lệ)</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -13563,7 +13563,7 @@
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doi tuong dang o trang thai confirmed. </t>
+          <t xml:space="preserve">Đối tượng đang ở trạng thái confirmed. </t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -13583,7 +13583,7 @@
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>trang thai sau khi goi = canceled</t>
+          <t>trạng thái sau khi gọi = canceled</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
@@ -13613,7 +13613,7 @@
       </c>
       <c r="S47" s="3" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T47" s="3" t="inlineStr">
@@ -13656,7 +13656,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai pending -&gt; shipping (KHONG hop le)</t>
+          <t>Chuyển trạng thái pending -&gt; shipping (KHÔNG hợp lệ)</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -13671,7 +13671,7 @@
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>Doi tuong dang o trang thai pending. Nhay coc trang thai</t>
+          <t>Đối tượng đang ở trạng thái pending. Nhảy cóc trạng thái</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>body.error chua Invalid state transition; trang thai KHONG doi</t>
+          <t>body.error chứa Invalid state transition; trạng thái KHÔNG đổi</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="S48" s="3" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T48" s="3" t="inlineStr">
@@ -13764,7 +13764,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai pending -&gt; delivered (KHONG hop le)</t>
+          <t>Chuyển trạng thái pending -&gt; delivered (KHÔNG hợp lệ)</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doi tuong dang o trang thai pending. </t>
+          <t xml:space="preserve">Đối tượng đang ở trạng thái pending. </t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>body.error chua Invalid state transition; trang thai KHONG doi</t>
+          <t>body.error chứa Invalid state transition; trạng thái KHÔNG đổi</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
@@ -13829,7 +13829,7 @@
       </c>
       <c r="S49" s="3" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T49" s="3" t="inlineStr">
@@ -13872,7 +13872,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai confirmed -&gt; pending (KHONG hop le)</t>
+          <t>Chuyển trạng thái confirmed -&gt; pending (KHÔNG hợp lệ)</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -13887,7 +13887,7 @@
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>Doi tuong dang o trang thai confirmed. Lui trang thai</t>
+          <t>Đối tượng đang ở trạng thái confirmed. Lùi trạng thái</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>body.error chua Invalid state transition; trang thai KHONG doi</t>
+          <t>body.error chứa Invalid state transition; trạng thái KHÔNG đổi</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
@@ -13937,7 +13937,7 @@
       </c>
       <c r="S50" s="3" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T50" s="3" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai confirmed -&gt; delivered (KHONG hop le)</t>
+          <t>Chuyển trạng thái confirmed -&gt; delivered (KHÔNG hợp lệ)</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -13995,7 +13995,7 @@
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doi tuong dang o trang thai confirmed. </t>
+          <t xml:space="preserve">Đối tượng đang ở trạng thái confirmed. </t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
@@ -14015,7 +14015,7 @@
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>body.error chua Invalid state transition; trang thai KHONG doi</t>
+          <t>body.error chứa Invalid state transition; trạng thái KHÔNG đổi</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
@@ -14045,7 +14045,7 @@
       </c>
       <c r="S51" s="3" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T51" s="3" t="inlineStr">
@@ -14088,7 +14088,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai shipping -&gt; pending (KHONG hop le)</t>
+          <t>Chuyển trạng thái shipping -&gt; pending (KHÔNG hợp lệ)</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -14103,7 +14103,7 @@
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doi tuong dang o trang thai shipping. </t>
+          <t xml:space="preserve">Đối tượng đang ở trạng thái shipping. </t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
@@ -14123,7 +14123,7 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>body.error chua Invalid state transition; trang thai KHONG doi</t>
+          <t>body.error chứa Invalid state transition; trạng thái KHÔNG đổi</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
@@ -14153,7 +14153,7 @@
       </c>
       <c r="S52" s="3" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T52" s="3" t="inlineStr">
@@ -14196,7 +14196,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai shipping -&gt; confirmed (KHONG hop le)</t>
+          <t>Chuyển trạng thái shipping -&gt; confirmed (KHÔNG hợp lệ)</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -14211,7 +14211,7 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doi tuong dang o trang thai shipping. </t>
+          <t xml:space="preserve">Đối tượng đang ở trạng thái shipping. </t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -14231,7 +14231,7 @@
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>body.error chua Invalid state transition; trang thai KHONG doi</t>
+          <t>body.error chứa Invalid state transition; trạng thái KHÔNG đổi</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
@@ -14261,7 +14261,7 @@
       </c>
       <c r="S53" s="3" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T53" s="3" t="inlineStr">
@@ -14304,7 +14304,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai shipping -&gt; canceled (KHONG hop le)</t>
+          <t>Chuyển trạng thái shipping -&gt; canceled (KHÔNG hợp lệ)</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -14319,7 +14319,7 @@
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doi tuong dang o trang thai shipping. </t>
+          <t xml:space="preserve">Đối tượng đang ở trạng thái shipping. </t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>don dang giao KHONG duoc tu huy boi khach hang</t>
+          <t>đơn đang giao KHÔNG được tự hủy bởi khách hàng</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S54" s="3" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T54" s="3" t="inlineStr">
@@ -14412,7 +14412,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai delivered -&gt; shipping (KHONG hop le)</t>
+          <t>Chuyển trạng thái delivered -&gt; shipping (KHÔNG hợp lệ)</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doi tuong dang o trang thai delivered. </t>
+          <t xml:space="preserve">Đối tượng đang ở trạng thái delivered. </t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
@@ -14447,7 +14447,7 @@
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>body.error chua Invalid state transition; trang thai KHONG doi</t>
+          <t>body.error chứa Invalid state transition; trạng thái KHÔNG đổi</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
@@ -14477,7 +14477,7 @@
       </c>
       <c r="S55" s="3" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T55" s="3" t="inlineStr">
@@ -14520,7 +14520,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai delivered -&gt; canceled (KHONG hop le)</t>
+          <t>Chuyển trạng thái delivered -&gt; canceled (KHÔNG hợp lệ)</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -14535,7 +14535,7 @@
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doi tuong dang o trang thai delivered. </t>
+          <t xml:space="preserve">Đối tượng đang ở trạng thái delivered. </t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
@@ -14555,7 +14555,7 @@
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>body.error chua Invalid state transition; trang thai KHONG doi</t>
+          <t>body.error chứa Invalid state transition; trạng thái KHÔNG đổi</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
@@ -14585,7 +14585,7 @@
       </c>
       <c r="S56" s="3" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T56" s="3" t="inlineStr">
@@ -14628,7 +14628,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai delivered -&gt; delivered (KHONG hop le)</t>
+          <t>Chuyển trạng thái delivered -&gt; delivered (KHÔNG hợp lệ)</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -14643,7 +14643,7 @@
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>Doi tuong dang o trang thai delivered. Trang thai cuoi - khong doi duoc nua</t>
+          <t>Đối tượng đang ở trạng thái delivered. Trạng thái cuối - không đổi được nữa</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -14663,7 +14663,7 @@
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>body.error chua Invalid state transition; trang thai KHONG doi</t>
+          <t>body.error chứa Invalid state transition; trạng thái KHÔNG đổi</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
@@ -14693,7 +14693,7 @@
       </c>
       <c r="S57" s="3" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T57" s="3" t="inlineStr">
@@ -14736,7 +14736,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai canceled -&gt; delivered (KHONG hop le)</t>
+          <t>Chuyển trạng thái canceled -&gt; delivered (KHÔNG hợp lệ)</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -14751,7 +14751,7 @@
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doi tuong dang o trang thai canceled. </t>
+          <t xml:space="preserve">Đối tượng đang ở trạng thái canceled. </t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
@@ -14771,7 +14771,7 @@
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>don da huy TUYET DOI khong duoc chuyen sang da giao</t>
+          <t>đơn đã hủy TUYỆT ĐỐI không được chuyển sang đã giao</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
@@ -14801,7 +14801,7 @@
       </c>
       <c r="S58" s="3" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T58" s="3" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai canceled -&gt; confirmed (KHONG hop le)</t>
+          <t>Chuyển trạng thái canceled -&gt; confirmed (KHÔNG hợp lệ)</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -14859,7 +14859,7 @@
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doi tuong dang o trang thai canceled. </t>
+          <t xml:space="preserve">Đối tượng đang ở trạng thái canceled. </t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
@@ -14879,7 +14879,7 @@
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>body.error chua Invalid state transition; trang thai KHONG doi</t>
+          <t>body.error chứa Invalid state transition; trạng thái KHÔNG đổi</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
@@ -14909,7 +14909,7 @@
       </c>
       <c r="S59" s="3" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T59" s="3" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai canceled -&gt; canceled (KHONG hop le)</t>
+          <t>Chuyển trạng thái canceled -&gt; canceled (KHÔNG hợp lệ)</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -14967,7 +14967,7 @@
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>Doi tuong dang o trang thai canceled. Huy 2 lan</t>
+          <t>Đối tượng đang ở trạng thái canceled. Hủy 2 lần</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
@@ -14987,7 +14987,7 @@
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>body.error chua Invalid state transition; trang thai KHONG doi</t>
+          <t>body.error chứa Invalid state transition; trạng thái KHÔNG đổi</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
@@ -15017,7 +15017,7 @@
       </c>
       <c r="S60" s="3" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T60" s="3" t="inlineStr">
@@ -15060,7 +15060,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai pending -&gt; invalid_value (KHONG hop le)</t>
+          <t>Chuyển trạng thái pending -&gt; invalid_value (KHÔNG hợp lệ)</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -15075,7 +15075,7 @@
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>Doi tuong dang o trang thai pending. Gia tri trang thai khong nam trong enum</t>
+          <t>Đối tượng đang ở trạng thái pending. Giá trị trạng thái không nằm trong enum</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
@@ -15095,7 +15095,7 @@
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>body.error chua Invalid state transition; trang thai KHONG doi</t>
+          <t>body.error chứa Invalid state transition; trạng thái KHÔNG đổi</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
@@ -15125,7 +15125,7 @@
       </c>
       <c r="S61" s="3" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T61" s="3" t="inlineStr">
@@ -15168,7 +15168,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai pending -&gt; confirmed_by_user (KHONG hop le)</t>
+          <t>Chuyển trạng thái pending -&gt; confirmed_by_user (KHÔNG hợp lệ)</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -15183,7 +15183,7 @@
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doi tuong dang o trang thai pending. </t>
+          <t xml:space="preserve">Đối tượng đang ở trạng thái pending. </t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
@@ -15203,7 +15203,7 @@
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>user thuong KHONG duoc doi trang thai don hang</t>
+          <t>user thường KHÔNG được đổi trạng thái đơn hàng</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
@@ -15233,7 +15233,7 @@
       </c>
       <c r="S62" s="3" t="inlineStr">
         <is>
-          <t>R3 - Gan sai ma SEC (SEC-05 -&gt; SEC-03). User thuong tu xac nhan don hang = thao tac admin khong kiem role -&gt; SEC-03, khong phai SEC-05.</t>
+          <t>R3 - Gan sai ma SEC (SEC-05 -&gt; SEC-03). User thường tự xác nhận đơn hàng = thao tác admin không kiểm role -&gt; SEC-03, không phải SEC-05.</t>
         </is>
       </c>
       <c r="T62" s="3" t="inlineStr">
@@ -15276,7 +15276,7 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>[SEC-05] SQLi qua ma giam gia</t>
+          <t>[SEC-05] SQLi qua mã giảm giá</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="M63" s="4" t="inlineStr">
         <is>
-          <t>response KHONG chua truong password (du plaintext hay hash); mat khau khong duoc luu plaintext</t>
+          <t>response KHÔNG chứa trường password (dù plaintext hay hash); mật khẩu không được lưu plaintext</t>
         </is>
       </c>
       <c r="N63" s="4" t="inlineStr">
@@ -15384,7 +15384,7 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>[-] Response checkout khong duoc lo thong tin noi bo</t>
+          <t>[-] Response checkout không được lộ thông tin nội bộ</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
@@ -15419,7 +15419,7 @@
       </c>
       <c r="M64" s="4" t="inlineStr">
         <is>
-          <t>body khong chua stack trace, ten bang, duong dan file</t>
+          <t>body không chứa stack trace, tên bảng, đường dẫn file</t>
         </is>
       </c>
       <c r="N64" s="4" t="inlineStr">
@@ -15449,7 +15449,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>R3 - Gan sai ma SEC (SEC-02 -&gt; -). Khong lo stack trace khong duoc SEC-01..07 phu.</t>
+          <t>R3 - Gan sai ma SEC (SEC-02 -&gt; -). Không lộ stack trace không được SEC-01..07 phủ.</t>
         </is>
       </c>
       <c r="T64" s="4" t="inlineStr">
@@ -15492,7 +15492,7 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>[SEC-02] Checkout khong kem token phai bi tu choi</t>
+          <t>[SEC-02] Checkout không kèm token phải bị từ chối</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
@@ -15527,7 +15527,7 @@
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>tra 403 khi token hop le nhung role != 'admin'; hanh dong admin KHONG duoc thuc hien</t>
+          <t>trả 403 khi token hợp lệ nhưng role != 'admin'; hành động admin KHÔNG được thực hiện</t>
         </is>
       </c>
       <c r="N65" s="4" t="inlineStr">
@@ -15557,7 +15557,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>R3 - Gan sai ma SEC (SEC-03 -&gt; SEC-02). Thieu JWT -&gt; SEC-02; SEC-03 danh rieng cho viec kiem role.</t>
+          <t>R3 - Gan sai ma SEC (SEC-03 -&gt; SEC-02). Thiếu JWT -&gt; SEC-02; SEC-03 dành riêng cho việc kiểm role.</t>
         </is>
       </c>
       <c r="T65" s="4" t="inlineStr">
@@ -15600,7 +15600,7 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>[SEC-02] Apply-coupon khong kem token phai bi tu choi</t>
+          <t>[SEC-02] Apply-coupon không kèm token phải bị từ chối</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
@@ -15635,7 +15635,7 @@
       </c>
       <c r="M66" s="4" t="inlineStr">
         <is>
-          <t>tra 403 khi token hop le nhung role != 'admin'; hanh dong admin KHONG duoc thuc hien</t>
+          <t>trả 403 khi token hợp lệ nhưng role != 'admin'; hành động admin KHÔNG được thực hiện</t>
         </is>
       </c>
       <c r="N66" s="4" t="inlineStr">
@@ -15708,7 +15708,7 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>[SEC-02] Token JWT bi sua chu ky phai bi tu choi</t>
+          <t>[SEC-02] Token JWT bị sửa chữ ký phải bị từ chối</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
@@ -15743,7 +15743,7 @@
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>tra 403 khi token hop le nhung role != 'admin'; hanh dong admin KHONG duoc thuc hien</t>
+          <t>trả 403 khi token hợp lệ nhưng role != 'admin'; hành động admin KHÔNG được thực hiện</t>
         </is>
       </c>
       <c r="N67" s="4" t="inlineStr">
@@ -15773,7 +15773,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>R3 - Gan sai ma SEC (SEC-03 -&gt; SEC-02). Token sai chu ky = token khong hop le -&gt; SEC-02.</t>
+          <t>R3 - Gan sai ma SEC (SEC-03 -&gt; SEC-02). Token sai chữ ký = token không hợp lệ -&gt; SEC-02.</t>
         </is>
       </c>
       <c r="T67" s="4" t="inlineStr">
@@ -15816,7 +15816,7 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>[SEC-02] Xem don hang cua nguoi khac qua GET /api/orders/:id</t>
+          <t>[SEC-02] Xem đơn hàng của người khác qua GET /api/orders/:id</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
@@ -15851,7 +15851,7 @@
       </c>
       <c r="M68" s="4" t="inlineStr">
         <is>
-          <t>khong tra ve dia chi, tong tien cua don hang nguoi khac</t>
+          <t>không trả về địa chỉ, tổng tiền của đơn hàng người khác</t>
         </is>
       </c>
       <c r="N68" s="4" t="inlineStr">
@@ -15881,7 +15881,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>R3 - Gan sai ma SEC (SEC-04 -&gt; SEC-02). GET /api/orders/:id thieu han middleware xac thuc -&gt; vi pham SEC-02. SEC-04 la escape XSS.</t>
+          <t>R3 - Gan sai ma SEC (SEC-04 -&gt; SEC-02). GET /api/orders/:id thiếu hẳn middleware xác thực -&gt; vi phạm SEC-02. SEC-04 là escape XSS.</t>
         </is>
       </c>
       <c r="T68" s="4" t="inlineStr">
@@ -15924,7 +15924,7 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>[SEC-02] Xem don hang khong kem token</t>
+          <t>[SEC-02] Xem đơn hàng không kèm token</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -15959,7 +15959,7 @@
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>payload HTML/script khong duoc luu tho; server tra ve ban da escape hoac tu choi (4xx)</t>
+          <t>payload HTML/script không được lưu thô; server trả về bản đã escape hoặc từ chối (4xx)</t>
         </is>
       </c>
       <c r="N69" s="4" t="inlineStr">
@@ -16032,7 +16032,7 @@
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>[SEC-02] Huy don hang cua nguoi khac</t>
+          <t>[SEC-02] Hủy đơn hàng của người khác</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
@@ -16067,7 +16067,7 @@
       </c>
       <c r="M70" s="4" t="inlineStr">
         <is>
-          <t>payload HTML/script khong duoc luu tho; server tra ve ban da escape hoac tu choi (4xx)</t>
+          <t>payload HTML/script không được lưu thô; server trả về bản đã escape hoặc từ chối (4xx)</t>
         </is>
       </c>
       <c r="N70" s="4" t="inlineStr">
@@ -16140,7 +16140,7 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>[SEC-03] User thuong goi endpoint admin doi trang thai don</t>
+          <t>[SEC-03] User thường gọi endpoint admin đổi trạng thái đơn</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
@@ -16175,7 +16175,7 @@
       </c>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>truy van dung parameterized query: payload SQLi bi coi la chuoi tim kiem thuong, khong doi ngu nghia cau lenh; khong tra HTML loi DB</t>
+          <t>truy vấn dùng parameterized query: payload SQLi bị coi là chuỗi tìm kiếm thường, không đổi ngữ nghĩa câu lệnh; không trả HTML lỗi DB</t>
         </is>
       </c>
       <c r="N71" s="4" t="inlineStr">
@@ -16248,7 +16248,7 @@
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>[SEC-03] User thuong xem toan bo don hang qua GET /api/admin/orders</t>
+          <t>[SEC-03] User thường xem toàn bộ đơn hàng qua GET /api/admin/orders</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
@@ -16283,7 +16283,7 @@
       </c>
       <c r="M72" s="4" t="inlineStr">
         <is>
-          <t>truy van dung parameterized query: payload SQLi bi coi la chuoi tim kiem thuong, khong doi ngu nghia cau lenh; khong tra HTML loi DB</t>
+          <t>truy vấn dùng parameterized query: payload SQLi bị coi là chuỗi tìm kiếm thường, không đổi ngữ nghĩa câu lệnh; không trả HTML lỗi DB</t>
         </is>
       </c>
       <c r="N72" s="4" t="inlineStr">
@@ -16356,7 +16356,7 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>[SEC-04] XSS trong shipping_address phai bi chan hoac escape</t>
+          <t>[SEC-04] XSS trong shipping_address phải bị chặn hoặc escape</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>truong role trong body bi bo qua; role cua tai khoan sau khi goi van la 'user'</t>
+          <t>trường role trong body bị bỏ qua; role của tài khoản sau khi gọi vẫn là 'user'</t>
         </is>
       </c>
       <c r="N73" s="4" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>[-] Gui kem status='delivered' khi checkout</t>
+          <t>[-] Gửi kèm status='delivered' khi checkout</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="M74" s="4" t="inlineStr">
         <is>
-          <t>don hang moi tao phai o trang thai 'pending', KHONG phai 'delivered'</t>
+          <t>đơn hàng mới tạo phải ở trạng thái 'pending', KHÔNG phải 'delivered'</t>
         </is>
       </c>
       <c r="N74" s="4" t="inlineStr">
@@ -16529,7 +16529,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>R3 - Gan sai ma SEC (SEC-06 -&gt; -). Mass assignment truong 'status' khong phai 'role' nen khong thuoc SEC-06; day la yeu cau FR-08/FR-10.</t>
+          <t>R3 - Gan sai ma SEC (SEC-06 -&gt; -). Mass assignment trường 'status' không phải 'role' nên không thuộc SEC-06; đây là yêu cầu FR-08/FR-10.</t>
         </is>
       </c>
       <c r="T74" s="4" t="inlineStr">
@@ -16572,7 +16572,7 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>[-] Ap cung 1 coupon 10 lan lien tiep phai bi chan boi usage limit</t>
+          <t>[-] Áp cùng 1 coupon 10 lần liên tiếp phải bị chặn bởi usage limit</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
@@ -16607,7 +16607,7 @@
       </c>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>tu lan thu N+1 phai bi tu choi theo usage_limit</t>
+          <t>từ lần thứ N+1 phải bị từ chối theo usage_limit</t>
         </is>
       </c>
       <c r="N75" s="4" t="inlineStr">
@@ -16637,7 +16637,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>R3 - Gan sai ma SEC (SEC-07 -&gt; -). Han muc su dung coupon la FR-09 dieu kien C5, khong nam trong SEC-01..07.</t>
+          <t>R3 - Gan sai ma SEC (SEC-07 -&gt; -). Hạn mức sử dụng coupon là FR-09 điều kiện C5, không nằm trong SEC-01..07.</t>
         </is>
       </c>
       <c r="T75" s="4" t="inlineStr">
@@ -16680,7 +16680,7 @@
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>[SEC-06] User thuong tu nang role='admin' roi doi trang thai don hang</t>
+          <t>[SEC-06] User thường tự nâng role='admin' rồi đổi trạng thái đơn hàng</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
@@ -16715,7 +16715,7 @@
       </c>
       <c r="M76" s="4" t="inlineStr">
         <is>
-          <t>PUT /api/users/me KHONG duoc phep doi role; role sau khi goi van la 'user'; buoc goi API admin sau do phai bi tu choi</t>
+          <t>PUT /api/users/me KHÔNG được phép đổi role; role sau khi gọi vẫn là 'user'; bước gọi API admin sau đó phải bị từ chối</t>
         </is>
       </c>
       <c r="N76" s="4" t="inlineStr">
@@ -16745,7 +16745,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>R3 - Gan sai ma SEC (SEC-07 -&gt; SEC-06). Da viet lai thanh chuoi leo thang quyen (xem luat R1). | R1 - Ky vong 429 khong co can cu trong SRS. DA SUA: thay bang chuoi leo thang quyen that su kiem duoc va vi pham SEC-06 - user thuong tu nang role='admin' qua PUT /api/users/me roi goi API admin doi trang thai don. Bug X-01 phat hien o STEP 0.</t>
+          <t>R3 - Gan sai ma SEC (SEC-07 -&gt; SEC-06). Đã viết lại thành chuỗi leo thang quyền (xem luật R1). | R1 - Kỳ vọng 429 không có căn cứ trong SRS. ĐÃ SỬA: thay bằng chuỗi leo thang quyền thật sự kiểm được và vi phạm SEC-06 - user thường tự nâng role='admin' qua PUT /api/users/me rồi gọi API admin đổi trạng thái đơn. Bug X-01 phát hiện ở STEP 0.</t>
         </is>
       </c>
       <c r="T76" s="4" t="inlineStr">
@@ -16788,7 +16788,7 @@
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Response 201 cua checkout khop schema { orderId: integer, message: string }</t>
+          <t>Response 201 của checkout khớp schema { orderId: integer, message: string }</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
@@ -16853,7 +16853,7 @@
       </c>
       <c r="S77" s="5" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T77" s="5" t="inlineStr">
@@ -16896,7 +16896,7 @@
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>Response loi cua checkout khop schema { error: string }</t>
+          <t>Response lỗi của checkout khớp schema { error: string }</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -16961,7 +16961,7 @@
       </c>
       <c r="S78" s="5" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T78" s="5" t="inlineStr">
@@ -17004,7 +17004,7 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Response cua apply-coupon khop schema { discount_amount: number, final_amount: number }</t>
+          <t>Response của apply-coupon khớp schema { discount_amount: number, final_amount: number }</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
@@ -17019,7 +17019,7 @@
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>Folder _setup da chay xong va da dat cac bien moi truong can thiet</t>
+          <t>Folder _setup đã chạy xong và đã đặt các biến môi trường cần thiết</t>
         </is>
       </c>
       <c r="J79" s="5" t="inlineStr">
@@ -17039,7 +17039,7 @@
       </c>
       <c r="M79" s="5" t="inlineStr">
         <is>
-          <t>discount_amount la number va &gt; 0 va &lt; total_amount</t>
+          <t>discount_amount là number và &gt; 0 và &lt; total_amount</t>
         </is>
       </c>
       <c r="N79" s="5" t="inlineStr">
@@ -17069,7 +17069,7 @@
       </c>
       <c r="S79" s="5" t="inlineStr">
         <is>
-          <t>R10 - Case dung bien Postman ({{...}}) nhung precondition chi ghi 'SUT da seed', khong noi bien do duoc dat o dau. Chay doc lap se that bai. DA SUA: ghi ro buoc _setup phai chay truoc.</t>
+          <t>R10 - Case dùng biến Postman ({{...}}) nhưng precondition chỉ ghi 'SUT da seed', không nói biến đó được đặt ở đâu. Chạy độc lập sẽ thất bại. ĐÃ SỬA: ghi rõ bước _setup phải chạy trước.</t>
         </is>
       </c>
       <c r="T79" s="5" t="inlineStr">
@@ -17112,7 +17112,7 @@
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Response cua GET /api/orders/:id khop schema don hang day du</t>
+          <t>Response của GET /api/orders/:id khớp schema đơn hàng đầy đủ</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -17147,7 +17147,7 @@
       </c>
       <c r="M80" s="5" t="inlineStr">
         <is>
-          <t>co id, user_id, total_amount (number), status (enum 5 gia tri), shipping_address</t>
+          <t>có id, user_id, total_amount (number), status (enum 5 giá trị), shipping_address</t>
         </is>
       </c>
       <c r="N80" s="5" t="inlineStr">
@@ -17177,7 +17177,7 @@
       </c>
       <c r="S80" s="5" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T80" s="5" t="inlineStr">
@@ -17220,7 +17220,7 @@
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>Truong status luon thuoc enum 5 gia tri hop le</t>
+          <t>Trường status luôn thuộc enum 5 giá trị hợp lệ</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
@@ -17255,7 +17255,7 @@
       </c>
       <c r="M81" s="5" t="inlineStr">
         <is>
-          <t>moi phan tu co status thuoc [pending,confirmed,shipping,delivered,canceled]</t>
+          <t>mỗi phần tử có status thuộc [pending,confirmed,shipping,delivered,canceled]</t>
         </is>
       </c>
       <c r="N81" s="5" t="inlineStr">
@@ -17285,7 +17285,7 @@
       </c>
       <c r="S81" s="5" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T81" s="5" t="inlineStr">
@@ -17328,7 +17328,7 @@
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>total_amount luon la number, khong bao gio la string</t>
+          <t>total_amount luôn là number, không bao giờ là string</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -17363,7 +17363,7 @@
       </c>
       <c r="M82" s="5" t="inlineStr">
         <is>
-          <t>typeof total_amount === 'number' cho moi phan tu</t>
+          <t>typeof total_amount === 'number' cho mọi phần tử</t>
         </is>
       </c>
       <c r="N82" s="5" t="inlineStr">
@@ -17393,7 +17393,7 @@
       </c>
       <c r="S82" s="5" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T82" s="5" t="inlineStr">
@@ -17436,7 +17436,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Checkout voi total_amount = 1 roi doc lai don hang de xac nhan so tien that su duoc luu</t>
+          <t>Checkout với total_amount = 1 rồi đọc lại đơn hàng để xác nhận số tiền thật sự được lưu</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -17451,7 +17451,7 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Gio hang co 1 san pham gia 30.000.000d. Da goi POST /api/checkout voi total_amount = 1</t>
+          <t>Giỏ hàng có 1 sản phẩm giá 30.000.000đ. Đã gọi POST /api/checkout với total_amount = 1</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -17471,7 +17471,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>total_amount cua don hang phai bang tong tinh tu gio hang (30000000), KHONG duoc bang 1; SRS FR-08: 'Backend phai tu tinh lai tong tien; khong chap nhan gia tri total_amount do client gui len'</t>
+          <t>total_amount của đơn hàng phải bằng tổng tính từ giỏ hàng (30000000), KHÔNG được bằng 1; SRS FR-08: 'Backend phải tự tính lại tổng tiền; không chấp nhận giá trị total_amount do client gửi lên'</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -17501,7 +17501,7 @@
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>Case do sinh vien tu viet sau khi doc ma nguon SUT; khong qua bo sinh tu dong.</t>
+          <t>Case do sinh viên tự viết sau khi đọc mã nguồn SUT; không qua bộ sinh tự động.</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
@@ -17516,7 +17516,7 @@
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>API - Bo sinh co case 'total_amount = 1 phai bi tu choi' nhung chi kiem ma tra ve cua chinh request checkout. SUT tra 200 nen case do da 'phat hien' duoc bug, dung. Nhung no khong do duoc MUC DO thiet hai. Chi khi doc lai don hang moi thay so 1 that su nam trong CSDL - tuc la mua duoc dien thoai 30 trieu voi gia 1 dong. Bang chung nay can request thu hai, ma bo sinh chi lam viec tren tung request doc lap.</t>
+          <t>API - Bộ sinh có case 'total_amount = 1 phải bị từ chối' nhưng chỉ kiểm mã trả về của chính request checkout. SUT trả 200 nên case đó đã 'phát hiện' được bug, đúng. Nhưng nó không đo được MỨC ĐỘ thiệt hại. Chỉ khi đọc lại đơn hàng mới thấy số 1 thật sự nằm trong CSDL - tức là mua được điện thoại 30 triệu với giá 1 đồng. Bằng chứng này cần request thứ hai, mà bộ sinh chỉ làm việc trên từng request độc lập.</t>
         </is>
       </c>
     </row>
@@ -17548,7 +17548,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Sau khi thanh toan thanh cong, gio hang phai duoc xoa</t>
+          <t>Sau khi thanh toán thành công, giỏ hàng phải được xóa</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -17563,7 +17563,7 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Da them san pham vao gio va goi POST /api/checkout thanh cong</t>
+          <t>Đã thêm sản phẩm vào giỏ và gọi POST /api/checkout thành công</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -17583,7 +17583,7 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>gio hang phai la mang rong sau checkout (SRS FR-08: 'Sau thanh toan thanh cong, gio hang duoc xoa')</t>
+          <t>giỏ hàng phải là mảng rỗng sau checkout (SRS FR-08: 'Sau thanh toán thành công, giỏ hàng được xóa')</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -17613,7 +17613,7 @@
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>Case do sinh vien tu viet sau khi doc ma nguon SUT; khong qua bo sinh tu dong.</t>
+          <t>Case do sinh viên tự viết sau khi đọc mã nguồn SUT; không qua bộ sinh tự động.</t>
         </is>
       </c>
       <c r="T84" s="2" t="inlineStr">
@@ -17628,7 +17628,7 @@
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>PROMPT - Prompt khoanh API-2 vao POST /api/checkout. Nhung mot yeu cau cua FR-08 lai duoc kiem o mot endpoint KHAC han (GET /api/cart). Bo sinh phan hoach theo endpoint nen khong co cho nao de dat case 'hau qua cua checkout len gio hang'. Day la gioi han cua cach to chuc spec theo endpoint thay vi theo yeu cau.</t>
+          <t>PROMPT - Prompt khoanh API-2 vào POST /api/checkout. Nhưng một yêu cầu của FR-08 lại được kiểm ở một endpoint KHÁC hẳn (GET /api/cart). Bộ sinh phân hoạch theo endpoint nên không có chỗ nào để đặt case 'hậu quả của checkout lên giỏ hàng'. Đây là giới hạn của cách tổ chức spec theo endpoint thay vì theo yêu cầu.</t>
         </is>
       </c>
     </row>
@@ -17655,12 +17655,12 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>State Transition (chuoi day du)</t>
+          <t>State Transition (chuỗi đầy đủ)</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>Chuoi day du pending -&gt; confirmed -&gt; shipping roi USER tu huy: buoc cuoi phai bi chan</t>
+          <t>Chuỗi đầy đủ pending -&gt; confirmed -&gt; shipping rồi USER tự hủy: bước cuối phải bị chặn</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
@@ -17675,7 +17675,7 @@
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>Don da di het chuoi: tao moi (pending) -&gt; admin confirm -&gt; admin chuyen shipping</t>
+          <t>Đơn đã đi hết chuỗi: tạo mới (pending) -&gt; admin confirm -&gt; admin chuyển shipping</t>
         </is>
       </c>
       <c r="J85" s="3" t="inlineStr">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
-          <t>phai tra 400; trang thai don van phai la 'shipping' sau khi goi; SRS FR-10: 'Khi don hang da o trang thai shipping, User khong duoc phep tu huy'</t>
+          <t>phải trả 400; trạng thái đơn vẫn phải là 'shipping' sau khi gọi; SRS FR-10: 'Khi đơn hàng đã ở trạng thái shipping, User không được phép tự hủy'</t>
         </is>
       </c>
       <c r="N85" s="3" t="inlineStr">
@@ -17725,7 +17725,7 @@
       </c>
       <c r="S85" s="3" t="inlineStr">
         <is>
-          <t>Case do sinh vien tu viet sau khi doc ma nguon SUT; khong qua bo sinh tu dong.</t>
+          <t>Case do sinh viên tự viết sau khi đọc mã nguồn SUT; không qua bộ sinh tự động.</t>
         </is>
       </c>
       <c r="T85" s="3" t="inlineStr">
@@ -17740,7 +17740,7 @@
       </c>
       <c r="V85" s="3" t="inlineStr">
         <is>
-          <t>API - Bo sinh phu bang chuyen trang thai theo tung O RIENG LE (0-switch): moi case dat don vao mot trang thai roi thu mot buoc chuyen. Nhung dua don ve trang thai 'shipping' doi hoi di qua DUNG hai buoc admin truoc do - mot chuoi 4 request. Muon phu day du phai chuyen sang 1-switch/n-switch coverage, la thu phai thiet ke tay chu bo sinh khong tu suy ra duoc tu bang trang thai.</t>
+          <t>API - Bộ sinh phủ bảng chuyển trạng thái theo từng Ô RIÊNG LẺ (0-switch): mỗi case đặt đơn vào một trạng thái rồi thử một bước chuyển. Nhưng đưa đơn về trạng thái 'shipping' đòi hỏi đi qua ĐÚNG hai bước admin trước đó - một chuỗi 4 request. Muốn phủ đầy đủ phải chuyển sang 1-switch/n-switch coverage, là thứ phải thiết kế tay chứ bộ sinh không tự suy ra được từ bảng trạng thái.</t>
         </is>
       </c>
     </row>
@@ -17772,7 +17772,7 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>Chuyen tu pending sang chinh pending phai bi tu choi</t>
+          <t>Chuyển từ pending sang chính pending phải bị từ chối</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
@@ -17787,7 +17787,7 @@
       </c>
       <c r="I86" s="3" t="inlineStr">
         <is>
-          <t>Don dang o trang thai pending</t>
+          <t>Đơn đang ở trạng thái pending</t>
         </is>
       </c>
       <c r="J86" s="3" t="inlineStr">
@@ -17807,7 +17807,7 @@
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>body.error chua 'Invalid state transition'; trang thai KHONG doi; so do FR-10 khong co mui ten nao tu mot trang thai ve chinh no</t>
+          <t>body.error chứa 'Invalid state transition'; trạng thái KHÔNG đổi; sơ đồ FR-10 không có mũi tên nào từ một trạng thái về chính nó</t>
         </is>
       </c>
       <c r="N86" s="3" t="inlineStr">
@@ -17837,7 +17837,7 @@
       </c>
       <c r="S86" s="3" t="inlineStr">
         <is>
-          <t>Case do sinh vien tu viet sau khi doc ma nguon SUT; khong qua bo sinh tu dong.</t>
+          <t>Case do sinh viên tự viết sau khi đọc mã nguồn SUT; không qua bộ sinh tự động.</t>
         </is>
       </c>
       <c r="T86" s="3" t="inlineStr">
@@ -17852,7 +17852,7 @@
       </c>
       <c r="V86" s="3" t="inlineStr">
         <is>
-          <t>MODEL - Bang chuyen trang thai trong spec liet ke cac cap (from, to) KHAC nhau; 5 o duong cheo (pending-&gt;pending, confirmed-&gt;confirmed, ...) bi bo trong vi truc quan chung 'khong phai mot buoc chuyen'. Do phu STA cua API-2 vi the dung o 20/25. Day dung la loai o hay bi bo sot trong thuc te, va cung la loai o hay gay loi that (mot request bi gui lai hai lan).</t>
+          <t>MODEL - Bảng chuyển trạng thái trong spec liệt kê các cặp (from, to) KHÁC nhau; 5 ô đường chéo (pending-&gt;pending, confirmed-&gt;confirmed, ...) bị bỏ trống vì trực quan chúng 'không phải một bước chuyển'. Độ phủ STA của API-2 vì thế dừng ở 20/25. Đây đúng là loại ô hay bị bỏ sót trong thực tế, và cũng là loại ô hay gây lỗi thật (một request bị gửi lại hai lần).</t>
         </is>
       </c>
     </row>
@@ -17919,7 +17919,7 @@
       </c>
       <c r="M87" s="4" t="inlineStr">
         <is>
-          <t>apply-coupon phai yeu cau JWT va lay user tu token (SRS FR-09 dieu kien C4); khong duoc lay user_id tu body; vong thu 3 phai bi tu choi vi da het luot</t>
+          <t>apply-coupon phải yêu cầu JWT và lấy user từ token (SRS FR-09 điều kiện C4); không được lấy user_id từ body; vòng thứ 3 phải bị từ chối vì đã hết lượt</t>
         </is>
       </c>
       <c r="N87" s="4" t="inlineStr">
@@ -17949,7 +17949,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>Case do sinh vien tu viet sau khi doc ma nguon SUT; khong qua bo sinh tu dong.</t>
+          <t>Case do sinh viên tự viết sau khi đọc mã nguồn SUT; không qua bộ sinh tự động.</t>
         </is>
       </c>
       <c r="T87" s="4" t="inlineStr">
@@ -17964,7 +17964,7 @@
       </c>
       <c r="V87" s="4" t="inlineStr">
         <is>
-          <t>MODEL - Bo sinh coi 'thieu tham so bat buoc' la mot lop khong hop le, nen sinh case 'thieu user_id -&gt; phai tra 400/401'. No khong nhan ra rang trong code, THIEU tham so nay lai la duong vong qua toan bo kiem tra han muc: nhanh `if (user_id)` bi bo qua han. Day la nghich ly 'bo bot du lieu de duoc nhieu quyen hon', chi thay duoc khi doc ma nguon chu khong suy ra tu hinh dang API.</t>
+          <t>MODEL - Bộ sinh coi 'thiếu tham số bắt buộc' là một lớp không hợp lệ, nên sinh case 'thiếu user_id -&gt; phải trả 400/401'. Nó không nhận ra rằng trong code, THIẾU tham số này lại là đường vòng qua toàn bộ kiểm tra hạn mức: nhánh `if (user_id)` bị bỏ qua hẳn. Đây là nghịch lý 'bỏ bớt dữ liệu để được nhiều quyền hơn', chỉ thấy được khi đọc mã nguồn chứ không suy ra từ hình dạng API.</t>
         </is>
       </c>
     </row>
@@ -17996,7 +17996,7 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>[-] POST /api/coupon-usage ghi nhan luot dung cho mot coupon_id khong ton tai</t>
+          <t>[-] POST /api/coupon-usage ghi nhận lượt dùng cho một coupon_id không tồn tại</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
@@ -18031,7 +18031,7 @@
       </c>
       <c r="M88" s="4" t="inlineStr">
         <is>
-          <t>phai tu choi coupon_id khong ton tai; bang coupon_usage KHONG duoc phat sinh ban ghi rac; ban ghi rac se lam sai phep dem han muc su dung cua FR-09 dieu kien C5</t>
+          <t>phải từ chối coupon_id không tồn tại; bảng coupon_usage KHÔNG được phát sinh bản ghi rác; bản ghi rác sẽ làm sai phép đếm hạn mức sử dụng của FR-09 điều kiện C5</t>
         </is>
       </c>
       <c r="N88" s="4" t="inlineStr">
@@ -18061,7 +18061,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>Case do sinh vien tu viet sau khi doc ma nguon SUT; khong qua bo sinh tu dong.</t>
+          <t>Case do sinh viên tự viết sau khi đọc mã nguồn SUT; không qua bộ sinh tự động.</t>
         </is>
       </c>
       <c r="T88" s="4" t="inlineStr">
@@ -18076,7 +18076,7 @@
       </c>
       <c r="V88" s="4" t="inlineStr">
         <is>
-          <t>SPECGAP - api_specification.md khong he liet ke endpoint POST /api/coupon-usage; no chi xuat hien trong server.js voi mot dong comment. Bo sinh doc dac ta nen khong biet endpoint nay ton tai. Day la loi 'endpoint khong duoc tai lieu hoa' - loai be mat tan cong ma kiem thu dua tren dac ta khong bao gio cham toi.</t>
+          <t>SPECGAP - api_specification.md không hề liệt kê endpoint POST /api/coupon-usage; nó chỉ xuất hiện trong server.js với một dòng comment. Bộ sinh đọc đặc tả nên không biết endpoint này tồn tại. Đây là lỗi 'endpoint không được tài liệu hóa' - loại bề mặt tấn công mà kiểm thử dựa trên đặc tả không bao giờ chạm tới.</t>
         </is>
       </c>
     </row>
@@ -18259,7 +18259,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>POST /api/products | name = SP Test 23127060 (ten hop le)</t>
+          <t>POST /api/products | name = SP Test 23127060 (tên hợp lệ)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -18274,7 +18274,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Da login bang tai khoan admin, co {{token_admin}}</t>
+          <t>Đã login bằng tài khoản admin, có {{token_admin}}</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -18294,7 +18294,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>body co id; GET lai san pham thay dung ten</t>
+          <t>body có id; GET lại sản phẩm thấy đúng tên</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -18324,7 +18324,7 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
@@ -18367,7 +18367,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>POST /api/products | name =  (ten rong)</t>
+          <t>POST /api/products | name =  (tên rỗng)</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -18382,7 +18382,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Da login bang tai khoan admin, co {{token_admin}}</t>
+          <t>Đã login bằng tài khoản admin, có {{token_admin}}</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -18402,7 +18402,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -18432,7 +18432,7 @@
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
@@ -18475,7 +18475,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>POST /api/products | name = - (ten null)</t>
+          <t>POST /api/products | name = - (tên null)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -18490,7 +18490,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Da login bang tai khoan admin, co {{token_admin}}</t>
+          <t>Đã login bằng tài khoản admin, có {{token_admin}}</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -18510,7 +18510,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -18540,7 +18540,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -18583,7 +18583,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>POST /api/products | name = &lt;thieu key&gt; (thieu key name)</t>
+          <t>POST /api/products | name = &lt;thieu key&gt; (thiếu key name)</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -18598,7 +18598,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Da login bang tai khoan admin, co {{token_admin}}</t>
+          <t>Đã login bằng tài khoản admin, có {{token_admin}}</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -18618,7 +18618,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -18648,7 +18648,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -18691,7 +18691,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>POST /api/products | name = 12345 (ten sai kieu (number))</t>
+          <t>POST /api/products | name = 12345 (tên sai kiểu (number))</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -18706,7 +18706,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Da login bang tai khoan admin, co {{token_admin}}</t>
+          <t>Đã login bằng tài khoản admin, có {{token_admin}}</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -18726,7 +18726,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -18756,7 +18756,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -18799,7 +18799,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>POST /api/products | name = A (BVA - 1 ky tu (duoi bien toi thieu))</t>
+          <t>POST /api/products | name = A (BVA - 1 ký tự (dưới biên tối thiểu))</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -18814,7 +18814,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Da login bang tai khoan admin, co {{token_admin}}</t>
+          <t>Đã login bằng tài khoản admin, có {{token_admin}}</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -18834,7 +18834,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -18864,7 +18864,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -18907,7 +18907,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>POST /api/products | name = A123456789A123456789A123456789A123456789 (BVA - dung 255 ky tu)</t>
+          <t>POST /api/products | name = A123456789A123456789A123456789A123456789 (BVA - đúng 255 ký tự)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -18922,7 +18922,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Da login bang tai khoan admin, co {{token_admin}}</t>
+          <t>Đã login bằng tài khoản admin, có {{token_admin}}</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -18942,7 +18942,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; khop schema thanh cong; VA doc lai tai nguyen de xac nhan gia tri luu dung bang gia tri da gui</t>
+          <t>body là JSON; khớp schema thành công; VA doc lai tai nguyen de xac nhan gia tri luu dung bang gia tri da gui</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -18972,7 +18972,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>R8 - Case thanh cong nhung chi kiem 'khop schema'. Thieu khang dinh gia tri that su duoc luu dung. DA SUA: bo sung buoc doc lai tai nguyen va so khop gia tri vua gui.</t>
+          <t>R8 - Case thành công nhưng chỉ kiểm 'khớp schema'. Thiếu khẳng định giá trị thật sự được lưu đúng. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên và so khớp giá trị vừa gửi.</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -19015,7 +19015,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>POST /api/products | name = A123456789A123456789A123456789A123456789 (BVA - 256 ky tu (vuot bien))</t>
+          <t>POST /api/products | name = A123456789A123456789A123456789A123456789 (BVA - 256 ký tự (vượt biên))</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -19030,7 +19030,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Da login bang tai khoan admin, co {{token_admin}}</t>
+          <t>Đã login bằng tài khoản admin, có {{token_admin}}</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -19050,7 +19050,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -19080,7 +19080,7 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
@@ -19123,7 +19123,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>POST /api/products | name = &lt;script&gt;alert('23127060')&lt;/script&gt; (stored XSS trong ten san pham)</t>
+          <t>POST /api/products | name = &lt;script&gt;alert('23127060')&lt;/script&gt; (stored XSS trong tên sản phẩm)</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -19138,7 +19138,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Da login bang tai khoan admin, co {{token_admin}}</t>
+          <t>Đã login bằng tài khoản admin, có {{token_admin}}</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -19158,7 +19158,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -19188,7 +19188,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>R3 - Gan sai ma SEC (SEC-06 -&gt; SEC-04). Stored XSS qua ten san pham -&gt; SEC-04.</t>
+          <t>R3 - Gan sai ma SEC (SEC-06 -&gt; SEC-04). Stored XSS qua tên sản phẩm -&gt; SEC-04.</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -19231,7 +19231,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>POST /api/products | name = San pham tieng Viet co dau 23127060 (ten co ky tu Unicode)</t>
+          <t>POST /api/products | name = San pham tieng Viet co dau 23127060 (tên có ký tự Unicode)</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -19246,7 +19246,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Da login bang tai khoan admin, co {{token_admin}}</t>
+          <t>Đã login bằng tài khoản admin, có {{token_admin}}</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -19266,7 +19266,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; khop schema thanh cong; VA doc lai tai nguyen de xac nhan gia tri luu dung bang gia tri da gui</t>
+          <t>body là JSON; khớp schema thành công; VA doc lai tai nguyen de xac nhan gia tri luu dung bang gia tri da gui</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -19296,7 +19296,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>R8 - Case thanh cong nhung chi kiem 'khop schema'. Thieu khang dinh gia tri that su duoc luu dung. DA SUA: bo sung buoc doc lai tai nguyen va so khop gia tri vua gui.</t>
+          <t>R8 - Case thành công nhưng chỉ kiểm 'khớp schema'. Thiếu khẳng định giá trị thật sự được lưu đúng. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên và so khớp giá trị vừa gửi.</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -19339,7 +19339,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>POST /api/products | price = 150000 (gia hop le)</t>
+          <t>POST /api/products | price = 150000 (giá hợp lệ)</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -19354,7 +19354,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Da login bang tai khoan admin, co {{token_admin}}</t>
+          <t>Đã login bằng tài khoản admin, có {{token_admin}}</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -19374,7 +19374,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; khop schema thanh cong; VA doc lai tai nguyen de xac nhan gia tri luu dung bang gia tri da gui</t>
+          <t>body là JSON; khớp schema thành công; VA doc lai tai nguyen de xac nhan gia tri luu dung bang gia tri da gui</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>R8 - Case thanh cong nhung chi kiem 'khop schema'. Thieu khang dinh gia tri that su duoc luu dung. DA SUA: bo sung buoc doc lai tai nguyen va so khop gia tri vua gui.</t>
+          <t>R8 - Case thành công nhưng chỉ kiểm 'khớp schema'. Thiếu khẳng định giá trị thật sự được lưu đúng. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên và so khớp giá trị vừa gửi.</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
@@ -19447,7 +19447,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>POST /api/products | price = -1000 (gia am)</t>
+          <t>POST /api/products | price = -1000 (giá âm)</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -19462,7 +19462,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Da login bang tai khoan admin, co {{token_admin}}</t>
+          <t>Đã login bằng tài khoản admin, có {{token_admin}}</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -19512,7 +19512,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -19555,7 +19555,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>POST /api/products | price = 0 (BVA - gia bang 0)</t>
+          <t>POST /api/products | price = 0 (BVA - giá bằng 0)</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -19570,7 +19570,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Da login bang tai khoan admin, co {{token_admin}}</t>
+          <t>Đã login bằng tài khoản admin, có {{token_admin}}</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -19590,7 +19590,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -19620,7 +19620,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>POST /api/products | price = 1 (BVA - gia 1 (bien duoi hop le))</t>
+          <t>POST /api/products | price = 1 (BVA - giá 1 (biên dưới hợp lệ))</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -19678,7 +19678,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Da login bang tai khoan admin, co {{token_admin}}</t>
+          <t>Đã login bằng tài khoản admin, có {{token_admin}}</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -19698,7 +19698,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; khop schema thanh cong; VA doc lai tai nguyen de xac nhan gia tri luu dung bang gia tri da gui</t>
+          <t>body là JSON; khớp schema thành công; VA doc lai tai nguyen de xac nhan gia tri luu dung bang gia tri da gui</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -19728,7 +19728,7 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>R8 - Case thanh cong nhung chi kiem 'khop schema'. Thieu khang dinh gia tri that su duoc luu dung. DA SUA: bo sung buoc doc lai tai nguyen va so khop gia tri vua gui.</t>
+          <t>R8 - Case thành công nhưng chỉ kiểm 'khớp schema'. Thiếu khẳng định giá trị thật sự được lưu đúng. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên và so khớp giá trị vừa gửi.</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
@@ -19771,7 +19771,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>POST /api/products | price = khong-phai-so (gia sai kieu (string))</t>
+          <t>POST /api/products | price = khong-phai-so (giá sai kiểu (string))</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -19786,7 +19786,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Da login bang tai khoan admin, co {{token_admin}}</t>
+          <t>Đã login bằng tài khoản admin, có {{token_admin}}</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -19806,7 +19806,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -19836,7 +19836,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -19879,7 +19879,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>POST /api/products | price = - (gia null)</t>
+          <t>POST /api/products | price = - (giá null)</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Da login bang tai khoan admin, co {{token_admin}}</t>
+          <t>Đã login bằng tài khoản admin, có {{token_admin}}</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -19914,7 +19914,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -19944,7 +19944,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -19987,7 +19987,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>POST /api/products | price = &lt;thieu key&gt; (thieu key price)</t>
+          <t>POST /api/products | price = &lt;thieu key&gt; (thiếu key price)</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -20002,7 +20002,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Da login bang tai khoan admin, co {{token_admin}}</t>
+          <t>Đã login bằng tài khoản admin, có {{token_admin}}</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -20022,7 +20022,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -20052,7 +20052,7 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
@@ -20095,7 +20095,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>POST /api/products | price = 999999999999999 (BVA - gia vuot gioi han)</t>
+          <t>POST /api/products | price = 999999999999999 (BVA - giá vượt giới hạn)</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -20110,7 +20110,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Da login bang tai khoan admin, co {{token_admin}}</t>
+          <t>Đã login bằng tài khoản admin, có {{token_admin}}</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -20130,7 +20130,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -20160,7 +20160,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
@@ -20203,7 +20203,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>POST /api/products | price = 150000.55 (gia co phan thap phan)</t>
+          <t>POST /api/products | price = 150000.55 (giá có phần thập phân)</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -20218,7 +20218,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Da login bang tai khoan admin, co {{token_admin}}</t>
+          <t>Đã login bằng tài khoản admin, có {{token_admin}}</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -20238,7 +20238,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; khop schema thanh cong; VA doc lai tai nguyen de xac nhan gia tri luu dung bang gia tri da gui</t>
+          <t>body là JSON; khớp schema thành công; VA doc lai tai nguyen de xac nhan gia tri luu dung bang gia tri da gui</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -20268,7 +20268,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>R8 - Case thanh cong nhung chi kiem 'khop schema'. Thieu khang dinh gia tri that su duoc luu dung. DA SUA: bo sung buoc doc lai tai nguyen va so khop gia tri vua gui.</t>
+          <t>R8 - Case thành công nhưng chỉ kiểm 'khớp schema'. Thiếu khẳng định giá trị thật sự được lưu đúng. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên và so khớp giá trị vừa gửi.</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -20311,7 +20311,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>POST /api/products | category_id = 999999 (danh muc khong ton tai - khoa ngoai khong duoc kiem tra)</t>
+          <t>POST /api/products | category_id = 999999 (danh mục không tồn tại - khóa ngoại không được kiểm tra)</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -20326,7 +20326,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Da login bang tai khoan admin, co {{token_admin}}</t>
+          <t>Đã login bằng tài khoản admin, có {{token_admin}}</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -20346,7 +20346,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -20376,7 +20376,7 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
@@ -20434,7 +20434,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Da login bang tai khoan admin, co {{token_admin}}</t>
+          <t>Đã login bằng tài khoản admin, có {{token_admin}}</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -20484,7 +20484,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -20527,7 +20527,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>POST /api/products | category_id = abc (category_id sai kieu)</t>
+          <t>POST /api/products | category_id = abc (category_id sai kiểu)</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -20542,7 +20542,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Da login bang tai khoan admin, co {{token_admin}}</t>
+          <t>Đã login bằng tài khoản admin, có {{token_admin}}</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -20562,7 +20562,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -20592,7 +20592,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -20635,7 +20635,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>POST /api/products | category_id = - (category_id null (khong bat buoc))</t>
+          <t>POST /api/products | category_id = - (category_id null (không bắt buộc))</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Da login bang tai khoan admin, co {{token_admin}}</t>
+          <t>Đã login bằng tài khoản admin, có {{token_admin}}</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -20670,7 +20670,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; khop schema thanh cong; VA doc lai tai nguyen de xac nhan gia tri luu dung bang gia tri da gui</t>
+          <t>body là JSON; khớp schema thành công; VA doc lai tai nguyen de xac nhan gia tri luu dung bang gia tri da gui</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -20700,7 +20700,7 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>R8 - Case thanh cong nhung chi kiem 'khop schema'. Thieu khang dinh gia tri that su duoc luu dung. DA SUA: bo sung buoc doc lai tai nguyen va so khop gia tri vua gui.</t>
+          <t>R8 - Case thành công nhưng chỉ kiểm 'khớp schema'. Thiếu khẳng định giá trị thật sự được lưu đúng. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên và so khớp giá trị vừa gửi.</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
@@ -20758,7 +20758,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Da login bang tai khoan admin, co {{token_admin}}</t>
+          <t>Đã login bằng tài khoản admin, có {{token_admin}}</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -20778,7 +20778,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -20866,7 +20866,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Da login bang tai khoan admin, co {{token_admin}}</t>
+          <t>Đã login bằng tài khoản admin, có {{token_admin}}</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -20886,7 +20886,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -20916,7 +20916,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>R3 - Gan sai ma SEC (SEC-06 -&gt; -). Path traversal trong imageUrl khong duoc bat ky ma SEC-01..07 nao phu. Van la test hop le, de SEC_Ref = '-'.</t>
+          <t>R3 - Gan sai ma SEC (SEC-06 -&gt; -). Path traversal trong imageUrl không được bất kỳ mã SEC-01..07 nào phủ. Vẫn là test hợp lệ, để SEC_Ref = '-'.</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -20959,7 +20959,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>POST /api/products | imageUrl = khong-phai-url (chuoi khong phai URL)</t>
+          <t>POST /api/products | imageUrl = khong-phai-url (chuỗi không phải URL)</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -20974,7 +20974,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Da login bang tai khoan admin, co {{token_admin}}</t>
+          <t>Đã login bằng tài khoản admin, có {{token_admin}}</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -20994,7 +20994,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -21024,7 +21024,7 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
@@ -21067,7 +21067,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>PUT /api/products/:id | id = 1 (id ton tai)</t>
+          <t>PUT /api/products/:id | id = 1 (id tồn tại)</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -21082,7 +21082,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>San pham id=1 ton tai</t>
+          <t>Sản phẩm id=1 tồn tại</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -21092,7 +21092,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>{"name":"SP Da Sua 23127060","price":180000,"description":"Da cap nhat","imageUrl":"https://example.com/b.png","category_id":1}</t>
+          <t>{"name":"SP Đã Sửa 23127060","price":180000,"description":"Da cap nhat","imageUrl":"https://example.com/b.png","category_id":1}</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -21102,7 +21102,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; khop schema thanh cong; VA doc lai tai nguyen de xac nhan gia tri luu dung bang gia tri da gui</t>
+          <t>body là JSON; khớp schema thành công; VA doc lai tai nguyen de xac nhan gia tri luu dung bang gia tri da gui</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -21132,7 +21132,7 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>R8 - Case thanh cong nhung chi kiem 'khop schema'. Thieu khang dinh gia tri that su duoc luu dung. DA SUA: bo sung buoc doc lai tai nguyen va so khop gia tri vua gui.</t>
+          <t>R8 - Case thành công nhưng chỉ kiểm 'khớp schema'. Thiếu khẳng định giá trị thật sự được lưu đúng. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên và so khớp giá trị vừa gửi.</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
@@ -21175,7 +21175,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>PUT /api/products/:id | id = 999999 (id khong ton tai - phai tra 404)</t>
+          <t>PUT /api/products/:id | id = 999999 (id không tồn tại - phải trả 404)</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -21190,7 +21190,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>San pham id=1 ton tai</t>
+          <t>Sản phẩm id=1 tồn tại</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -21200,7 +21200,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>{"name":"SP Da Sua 23127060","price":180000,"description":"Da cap nhat","imageUrl":"https://example.com/b.png","category_id":1}</t>
+          <t>{"name":"SP Đã Sửa 23127060","price":180000,"description":"Da cap nhat","imageUrl":"https://example.com/b.png","category_id":1}</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -21240,7 +21240,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -21298,7 +21298,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>San pham id=1 ton tai</t>
+          <t>Sản phẩm id=1 tồn tại</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -21308,7 +21308,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>{"name":"SP Da Sua 23127060","price":180000,"description":"Da cap nhat","imageUrl":"https://example.com/b.png","category_id":1}</t>
+          <t>{"name":"SP Đã Sửa 23127060","price":180000,"description":"Da cap nhat","imageUrl":"https://example.com/b.png","category_id":1}</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -21318,7 +21318,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -21348,7 +21348,7 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
@@ -21406,7 +21406,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>San pham id=1 ton tai</t>
+          <t>Sản phẩm id=1 tồn tại</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -21416,7 +21416,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>{"name":"SP Da Sua 23127060","price":180000,"description":"Da cap nhat","imageUrl":"https://example.com/b.png","category_id":1}</t>
+          <t>{"name":"SP Đã Sửa 23127060","price":180000,"description":"Da cap nhat","imageUrl":"https://example.com/b.png","category_id":1}</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -21426,7 +21426,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -21456,7 +21456,7 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
@@ -21499,7 +21499,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>PUT /api/products/:id | id = abc (id khong phai so)</t>
+          <t>PUT /api/products/:id | id = abc (id không phải số)</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -21514,7 +21514,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>San pham id=1 ton tai</t>
+          <t>Sản phẩm id=1 tồn tại</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -21524,7 +21524,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>{"name":"SP Da Sua 23127060","price":180000,"description":"Da cap nhat","imageUrl":"https://example.com/b.png","category_id":1}</t>
+          <t>{"name":"SP Đã Sửa 23127060","price":180000,"description":"Da cap nhat","imageUrl":"https://example.com/b.png","category_id":1}</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -21534,7 +21534,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -21564,7 +21564,7 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
@@ -21622,7 +21622,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>San pham id=1 ton tai</t>
+          <t>Sản phẩm id=1 tồn tại</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -21632,7 +21632,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>{"name":"SP Da Sua 23127060","price":180000,"description":"Da cap nhat","imageUrl":"https://example.com/b.png","category_id":1}</t>
+          <t>{"name":"SP Đã Sửa 23127060","price":180000,"description":"Da cap nhat","imageUrl":"https://example.com/b.png","category_id":1}</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -21642,7 +21642,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -21715,7 +21715,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>PUT /api/products/:id | description = &lt;thieu key&gt; (PUT khong gui description - KHONG duoc ghi de thanh null)</t>
+          <t>PUT /api/products/:id | description = &lt;thieu key&gt; (PUT không gửi description - KHÔNG được ghi đè thành null)</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -21730,7 +21730,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>San pham id=1 ton tai</t>
+          <t>Sản phẩm id=1 tồn tại</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -21740,7 +21740,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>{"name":"SP Da Sua 23127060","price":180000,"imageUrl":"https://example.com/b.png","category_id":1}</t>
+          <t>{"name":"SP Đã Sửa 23127060","price":180000,"imageUrl":"https://example.com/b.png","category_id":1}</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -21750,7 +21750,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>GET lai san pham: description phai giu nguyen gia tri cu</t>
+          <t>GET lại sản phẩm: description phải giữ nguyên giá trị cũ</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -21780,7 +21780,7 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
@@ -21838,7 +21838,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>San pham id=1 ton tai</t>
+          <t>Sản phẩm id=1 tồn tại</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -21848,7 +21848,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>{"name":"SP Da Sua 23127060","price":180000,"description":"Mo ta moi 23127060","imageUrl":"https://example.com/b.png","category_id":1}</t>
+          <t>{"name":"SP Đã Sửa 23127060","price":180000,"description":"Mo ta moi 23127060","imageUrl":"https://example.com/b.png","category_id":1}</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -21858,7 +21858,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; khop schema thanh cong; VA doc lai tai nguyen de xac nhan gia tri luu dung bang gia tri da gui</t>
+          <t>body là JSON; khớp schema thành công; VA doc lai tai nguyen de xac nhan gia tri luu dung bang gia tri da gui</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -21888,7 +21888,7 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>R8 - Case thanh cong nhung chi kiem 'khop schema'. Thieu khang dinh gia tri that su duoc luu dung. DA SUA: bo sung buoc doc lai tai nguyen va so khop gia tri vua gui.</t>
+          <t>R8 - Case thành công nhưng chỉ kiểm 'khớp schema'. Thiếu khẳng định giá trị thật sự được lưu đúng. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên và so khớp giá trị vừa gửi.</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
@@ -21931,7 +21931,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>PUT /api/products/:id | description = &lt;img src=x onerror=alert('23127060')&gt; (stored XSS trong mo ta (FE dung dangerouslySetInnerHTML))</t>
+          <t>PUT /api/products/:id | description = &lt;img src=x onerror=alert('23127060')&gt; (stored XSS trong mô tả (FE dùng dangerouslySetInnerHTML))</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -21946,7 +21946,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>San pham id=1 ton tai</t>
+          <t>Sản phẩm id=1 tồn tại</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -21956,7 +21956,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>{"name":"SP Da Sua 23127060","price":180000,"description":"&lt;img src=x onerror=alert('23127060')&gt;","imageUrl":"https://example.com/b.png","category_id":1}</t>
+          <t>{"name":"SP Đã Sửa 23127060","price":180000,"description":"&lt;img src=x onerror=alert('23127060')&gt;","imageUrl":"https://example.com/b.png","category_id":1}</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -21966,7 +21966,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -22039,7 +22039,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>DELETE /api/products/:id | id = 3 (xoa san pham ton tai)</t>
+          <t>DELETE /api/products/:id | id = 3 (xóa sản phẩm tồn tại)</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -22054,7 +22054,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>San pham id=3 ton tai</t>
+          <t>Sản phẩm id=3 tồn tại</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -22074,7 +22074,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>GET lai id=3 phai tra 404</t>
+          <t>GET lại id=3 phải trả 404</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -22104,7 +22104,7 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
@@ -22147,7 +22147,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>DELETE /api/products/:id | id = 999999 (xoa id khong ton tai - phai 404)</t>
+          <t>DELETE /api/products/:id | id = 999999 (xóa id không tồn tại - phải 404)</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>San pham id=3 ton tai</t>
+          <t>Sản phẩm id=3 tồn tại</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -22182,7 +22182,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -22212,7 +22212,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
@@ -22255,7 +22255,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>DELETE /api/products/:id | id = 3 (xoa lan thu 2 cung id)</t>
+          <t>DELETE /api/products/:id | id = 3 (xóa lần thứ 2 cùng id)</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -22270,7 +22270,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>San pham id=3 ton tai</t>
+          <t>Sản phẩm id=3 tồn tại</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -22290,7 +22290,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error; VA doc lai tai nguyen sau khi goi de xac nhan du lieu KHONG bi thay doi</t>
+          <t>body là JSON; có trường error; VÀ đọc lại tài nguyên sau khi gọi để xác nhận dữ liệu KHÔNG bị thay đổi</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -22320,7 +22320,7 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>R7 - Case tu choi mot thao tac GHI nhung chi kiem 'co truong error'. Thieu phan quan trong nhat: chung minh THAO TAC DA KHONG XAY RA. Mot API tra 400 roi van ghi vao CSDL se pass case nay. DA SUA: bo sung buoc doc lai tai nguyen sau khi goi.</t>
+          <t>R7 - Case từ chối một thao tác GHI nhưng chỉ kiểm 'có trường error'. Thiếu phần quan trọng nhất: chứng minh THAO TÁC ĐÃ KHÔNG XẢY RA. Một API trả 400 rồi vẫn ghi vào CSDL sẽ pass case này. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên sau khi gọi.</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
@@ -22363,7 +22363,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>DELETE /api/products/:id (xoa san pham vat thu do _setup tao ra)</t>
+          <t>DELETE /api/products/:id (xóa sản phẩm vật thử do _setup tạo ra)</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -22378,7 +22378,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>San pham id=3 ton tai</t>
+          <t>Sản phẩm id=3 tồn tại</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -22398,7 +22398,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>body co message; GET lai san pham do sau khi xoa KHONG duoc tra ve du lieu (bug C-04 tra 200 {})</t>
+          <t>body có message; GET lại sản phẩm đó sau khi xóa KHÔNG được trả về dữ liệu (bug C-04 trả 200 {})</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -22428,7 +22428,7 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>R2 - Ky vong 409 khong co can cu: SRS FR-15 chi noi 'Admin co the Them/Xem/Sua/Xoa san pham', khong he dat rang buoc khoa ngoai giua san pham va don hang. AI suy dien tu kinh nghiem CSDL. DA SUA: ky vong 200 (xoa thanh cong) va bo sung khang dinh san pham thuc su bien mat.</t>
+          <t>R2 - Kỳ vọng 409 không có căn cứ: SRS FR-15 chỉ nói 'Admin có thể Thêm/Xem/Sửa/Xóa sản phẩm', không hề đặt ràng buộc khóa ngoại giữa sản phẩm và đơn hàng. AI suy diễn từ kinh nghiệm CSDL. ĐÃ SỬA: kỳ vọng 200 (xóa thành công) và bổ sung khẳng định sản phẩm thực sự biến mất.</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
@@ -22471,7 +22471,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>GET /api/products | search = Laptop (tu khoa binh thuong)</t>
+          <t>GET /api/products | search = Laptop (từ khóa bình thường)</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -22486,7 +22486,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>DB da seed san pham</t>
+          <t>DB đã seed sản phẩm</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -22506,7 +22506,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>tra ve mang; moi phan tu co name chua 'Laptop'</t>
+          <t>trả về mảng; mỗi phần tử có name chứa 'Laptop'</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -22536,7 +22536,7 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
@@ -22579,7 +22579,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>GET /api/products | search =  (tu khoa rong - tra ve tat ca)</t>
+          <t>GET /api/products | search =  (từ khóa rỗng - trả về tất cả)</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -22594,7 +22594,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>DB da seed san pham</t>
+          <t>DB đã seed sản phẩm</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -22614,7 +22614,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; khop schema thanh cong; VA doc lai tai nguyen de xac nhan gia tri luu dung bang gia tri da gui</t>
+          <t>body là JSON; khớp schema thành công; VA doc lai tai nguyen de xac nhan gia tri luu dung bang gia tri da gui</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -22644,7 +22644,7 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>R8 - Case thanh cong nhung chi kiem 'khop schema'. Thieu khang dinh gia tri that su duoc luu dung. DA SUA: bo sung buoc doc lai tai nguyen va so khop gia tri vua gui.</t>
+          <t>R8 - Case thành công nhưng chỉ kiểm 'khớp schema'. Thiếu khẳng định giá trị thật sự được lưu đúng. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên và so khớp giá trị vừa gửi.</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
@@ -22687,7 +22687,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>GET /api/products | search = KhongTonTai23127060 (khong co ket qua - phai tra mang rong chu khong loi)</t>
+          <t>GET /api/products | search = KhongTonTai23127060 (không có kết quả - phải trả mảng rỗng chứ không lỗi)</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -22702,7 +22702,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>DB da seed san pham</t>
+          <t>DB đã seed sản phẩm</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -22722,7 +22722,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>body la mang rong []</t>
+          <t>body là mảng rỗng []</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -22752,7 +22752,7 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
@@ -22795,7 +22795,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>GET /api/products | search = %27 (1 dau nhay don lam vo cau SQL)</t>
+          <t>GET /api/products | search = %27 (1 dấu nháy đơn làm vỡ câu SQL)</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -22810,7 +22810,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>DB da seed san pham</t>
+          <t>DB đã seed sản phẩm</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -22830,7 +22830,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>khong tra 500; khong tra HTML</t>
+          <t>không trả 500; không trả HTML</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -22860,7 +22860,7 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>R3 - Gan sai ma SEC (SEC-01 -&gt; SEC-05). Lam vo cau SQL bang mot dau nhay don -&gt; bang chung truc tiep cua viec noi chuoi -&gt; SEC-05.</t>
+          <t>R3 - Gan sai ma SEC (SEC-01 -&gt; SEC-05). Làm vỡ câu SQL bằng một dấu nháy đơn -&gt; bằng chứng trực tiếp của việc nối chuỗi -&gt; SEC-05.</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
@@ -22903,7 +22903,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>GET /api/products | search = %25%27%20OR%20%271%27%3D%271 (SQLi OR 1=1 - lay toan bo san pham)</t>
+          <t>GET /api/products | search = %25%27%20OR%20%271%27%3D%271 (SQLi OR 1=1 - lấy toàn bộ sản phẩm)</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -22918,7 +22918,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>DB da seed san pham</t>
+          <t>DB đã seed sản phẩm</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -22938,7 +22938,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; co truong error</t>
+          <t>body là JSON; có trường error</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -23011,7 +23011,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>GET /api/products | search = %25%27%20UNION%20SELECT%20id%2Cemail%2Cp (SQLi UNION doc bang users)</t>
+          <t>GET /api/products | search = %25%27%20UNION%20SELECT%20id%2Cemail%2Cp (SQLi UNION đọc bảng users)</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -23026,7 +23026,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>DB da seed san pham</t>
+          <t>DB đã seed sản phẩm</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -23046,7 +23046,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>response KHONG chua email hoac password cua user</t>
+          <t>response KHÔNG chứa email hoặc password của user</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -23134,7 +23134,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>DB da seed san pham</t>
+          <t>DB đã seed sản phẩm</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -23154,7 +23154,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>bang products van con; GET /api/products sau do van hoat dong</t>
+          <t>bảng products vẫn còn; GET /api/products sau đó vẫn hoạt động</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -23227,7 +23227,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>GET /api/products | search = %3Cscript%3Ealert(1)%3C%2Fscript%3E (reflected XSS trong tu khoa)</t>
+          <t>GET /api/products | search = %3Cscript%3Ealert(1)%3C%2Fscript%3E (reflected XSS trong từ khóa)</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -23242,7 +23242,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>DB da seed san pham</t>
+          <t>DB đã seed sản phẩm</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -23262,7 +23262,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>response khong echo lai the script chua escape</t>
+          <t>response không echo lại thẻ script chưa escape</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -23335,7 +23335,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>GET /api/products | search = aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa (BVA - tu khoa rat dai)</t>
+          <t>GET /api/products | search = aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa (BVA - từ khóa rất dài)</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -23350,7 +23350,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>DB da seed san pham</t>
+          <t>DB đã seed sản phẩm</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -23370,7 +23370,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>body la JSON; khop schema thanh cong; VA doc lai tai nguyen de xac nhan gia tri luu dung bang gia tri da gui</t>
+          <t>body là JSON; khớp schema thành công; VA doc lai tai nguyen de xac nhan gia tri luu dung bang gia tri da gui</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -23400,7 +23400,7 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>R8 - Case thanh cong nhung chi kiem 'khop schema'. Thieu khang dinh gia tri that su duoc luu dung. DA SUA: bo sung buoc doc lai tai nguyen va so khop gia tri vua gui.</t>
+          <t>R8 - Case thành công nhưng chỉ kiểm 'khớp schema'. Thiếu khẳng định giá trị thật sự được lưu đúng. ĐÃ SỬA: bổ sung bước đọc lại tài nguyên và so khớp giá trị vừa gửi.</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
@@ -23443,7 +23443,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>GET /api/products/:id | id = 1 (id le - price phai la number)</t>
+          <t>GET /api/products/:id | id = 1 (id lẻ - price phải là number)</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -23458,7 +23458,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>SUT da seed</t>
+          <t>SUT đã seed</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -23508,7 +23508,7 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
@@ -23551,7 +23551,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>GET /api/products/:id | id = 2 (id chan - price bi chuyen thanh string)</t>
+          <t>GET /api/products/:id | id = 2 (id chẵn - price bị chuyển thành string)</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -23566,7 +23566,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>SUT da seed</t>
+          <t>SUT đã seed</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -23586,7 +23586,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>typeof price === 'number' (hien tai la string)</t>
+          <t>typeof price === 'number' (hiện tại là string)</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -23616,7 +23616,7 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
@@ -23659,7 +23659,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>GET /api/products/:id | id = 999999 (id khong ton tai - phai 404 chu khong phai 200 {})</t>
+          <t>GET /api/products/:id | id = 999999 (id không tồn tại - phải 404 chứ không phải 200 {})</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>SUT da seed</t>
+          <t>SUT đã seed</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -23694,7 +23694,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>status 404; body co truong error</t>
+          <t>status 404; body có trường error</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
@@ -23767,7 +23767,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai NOT_EXIST -&gt; CREATED (hop le)</t>
+          <t>Chuyển trạng thái NOT_EXIST -&gt; CREATED (hợp lệ)</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -23782,7 +23782,7 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doi tuong dang o trang thai NOT_EXIST. </t>
+          <t xml:space="preserve">Đối tượng đang ở trạng thái NOT_EXIST. </t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>tra 201 kem Location hoac id; GET lai thay san pham</t>
+          <t>trả 201 kèm Location hoặc id; GET lại thấy sản phẩm</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
@@ -23832,7 +23832,7 @@
       </c>
       <c r="S53" s="3" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T53" s="3" t="inlineStr">
@@ -23875,7 +23875,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai CREATED -&gt; UPDATED (hop le)</t>
+          <t>Chuyển trạng thái CREATED -&gt; UPDATED (hợp lệ)</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -23890,7 +23890,7 @@
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doi tuong dang o trang thai CREATED. </t>
+          <t xml:space="preserve">Đối tượng đang ở trạng thái CREATED. </t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
@@ -23910,7 +23910,7 @@
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>trang thai sau khi goi = UPDATED</t>
+          <t>trạng thái sau khi gọi = UPDATED</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
@@ -23940,7 +23940,7 @@
       </c>
       <c r="S54" s="3" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T54" s="3" t="inlineStr">
@@ -23983,7 +23983,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai UPDATED -&gt; DELETED (hop le)</t>
+          <t>Chuyển trạng thái UPDATED -&gt; DELETED (hợp lệ)</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -23998,7 +23998,7 @@
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doi tuong dang o trang thai UPDATED. </t>
+          <t xml:space="preserve">Đối tượng đang ở trạng thái UPDATED. </t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
@@ -24018,7 +24018,7 @@
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>trang thai sau khi goi = DELETED</t>
+          <t>trạng thái sau khi gọi = DELETED</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
@@ -24048,7 +24048,7 @@
       </c>
       <c r="S55" s="3" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T55" s="3" t="inlineStr">
@@ -24091,7 +24091,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai DELETED -&gt; READ (KHONG hop le)</t>
+          <t>Chuyển trạng thái DELETED -&gt; READ (KHÔNG hợp lệ)</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -24106,7 +24106,7 @@
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doi tuong dang o trang thai DELETED. </t>
+          <t xml:space="preserve">Đối tượng đang ở trạng thái DELETED. </t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
@@ -24126,7 +24126,7 @@
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>phai 404, khong duoc tra 200 voi body rong</t>
+          <t>phải 404, không được trả 200 với body rỗng</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
@@ -24156,7 +24156,7 @@
       </c>
       <c r="S56" s="3" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T56" s="3" t="inlineStr">
@@ -24199,7 +24199,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai DELETED -&gt; UPDATED (KHONG hop le)</t>
+          <t>Chuyển trạng thái DELETED -&gt; UPDATED (KHÔNG hợp lệ)</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -24214,7 +24214,7 @@
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doi tuong dang o trang thai DELETED. </t>
+          <t xml:space="preserve">Đối tượng đang ở trạng thái DELETED. </t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>khong duoc sua san pham da xoa</t>
+          <t>không được sửa sản phẩm đã xóa</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
@@ -24264,7 +24264,7 @@
       </c>
       <c r="S57" s="3" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T57" s="3" t="inlineStr">
@@ -24307,7 +24307,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai DELETED -&gt; DELETED (KHONG hop le)</t>
+          <t>Chuyển trạng thái DELETED -&gt; DELETED (KHÔNG hợp lệ)</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -24322,7 +24322,7 @@
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doi tuong dang o trang thai DELETED. </t>
+          <t xml:space="preserve">Đối tượng đang ở trạng thái DELETED. </t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
@@ -24342,7 +24342,7 @@
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>xoa lan 2 phai 404</t>
+          <t>xóa lần 2 phải 404</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
@@ -24372,7 +24372,7 @@
       </c>
       <c r="S58" s="3" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T58" s="3" t="inlineStr">
@@ -24415,7 +24415,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>Tao san pham trung ten voi san pham da co (SRS khong cam)</t>
+          <t>Tạo sản phẩm trùng tên với sản phẩm đã có (SRS không cấm)</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -24430,7 +24430,7 @@
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>Doi tuong dang o trang thai CREATED. Tao trung ten san pham</t>
+          <t>Đối tượng đang ở trạng thái CREATED. Tạo trùng tên sản phẩm</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
@@ -24450,7 +24450,7 @@
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>tao thanh cong; id tra ve khac id cua san pham dau tien; SRS khong cam trung ten</t>
+          <t>tạo thành công; id trả về khác id của sản phẩm đầu tiên; SRS không cấm trùng tên</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
@@ -24480,7 +24480,7 @@
       </c>
       <c r="S59" s="3" t="inlineStr">
         <is>
-          <t>R2 - Ky vong 409 khong co can cu: SRS khong yeu cau ten san pham duy nhat, va cot 'name' trong database.js khong co rang buoc UNIQUE. DA SUA: ky vong 201 (tao thanh cong) va chuyen trong tam sang dieu kiem duoc - hai ban ghi phai co id khac nhau.</t>
+          <t>R2 - Kỳ vọng 409 không có căn cứ: SRS không yêu cầu tên sản phẩm duy nhất, và cột 'name' trong database.js không có ràng buộc UNIQUE. ĐÃ SỬA: kỳ vọng 201 (tạo thành công) và chuyển trọng tâm sang điều kiểm được - hai bản ghi phải có id khác nhau.</t>
         </is>
       </c>
       <c r="T59" s="3" t="inlineStr">
@@ -24523,7 +24523,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Chuyen trang thai CREATED -&gt; IN_SEARCH (hop le)</t>
+          <t>Chuyển trạng thái CREATED -&gt; IN_SEARCH (hợp lệ)</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -24538,7 +24538,7 @@
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doi tuong dang o trang thai CREATED. </t>
+          <t xml:space="preserve">Đối tượng đang ở trạng thái CREATED. </t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
@@ -24558,7 +24558,7 @@
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>san pham vua tao xuat hien trong ket qua tim kiem</t>
+          <t>sản phẩm vừa tạo xuất hiện trong kết quả tìm kiếm</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
@@ -24588,7 +24588,7 @@
       </c>
       <c r="S60" s="3" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T60" s="3" t="inlineStr">
@@ -24631,7 +24631,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>Sau khi DELETE, san pham khong duoc con trong ket qua GET /api/products?search=</t>
+          <t>Sau khi DELETE, sản phẩm không được còn trong kết quả GET /api/products?search=</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -24646,7 +24646,7 @@
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doi tuong dang o trang thai DELETED. </t>
+          <t xml:space="preserve">Đối tượng đang ở trạng thái DELETED. </t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
@@ -24666,7 +24666,7 @@
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>HTTP 200 voi mang ket qua; mang KHONG duoc chua san pham vua bi xoa</t>
+          <t>HTTP 200 với mảng kết quả; mảng KHÔNG được chứa sản phẩm vừa bị xóa</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
@@ -24696,7 +24696,7 @@
       </c>
       <c r="S61" s="3" t="inlineStr">
         <is>
-          <t>R4 - Mau thuan noi tai: danh dau KHONG hop le nhung ky vong 200. Ngoai ra 'IN_SEARCH' khong phai mot trang thai cua vong doi tai nguyen ma la mot phep doc. DA SUA: giu phep kiem (san pham da xoa khong duoc xuat hien trong ket qua tim kiem) nhung phat bieu lai cho dung: ky vong 200 voi mang KHONG chua san pham da xoa.</t>
+          <t>R4 - Mâu thuẫn nội tại: đánh dấu KHÔNG hợp lệ nhưng kỳ vọng 200. Ngoài ra 'IN_SEARCH' không phải một trạng thái của vòng đời tài nguyên mà là một phép đọc. ĐÃ SỬA: giữ phép kiểm (sản phẩm đã xóa không được xuất hiện trong kết quả tìm kiếm) nhưng phát biểu lại cho đúng: kỳ vọng 200 với mảng KHÔNG chứa sản phẩm đã xóa.</t>
         </is>
       </c>
       <c r="T61" s="3" t="inlineStr">
@@ -24739,7 +24739,7 @@
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>[SEC-05] UNION SELECT doc bang users qua ?search</t>
+          <t>[SEC-05] UNION SELECT đọc bảng users qua ?search</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
@@ -24774,7 +24774,7 @@
       </c>
       <c r="M62" s="4" t="inlineStr">
         <is>
-          <t>response KHONG chua email/password cua user; khong tra 500</t>
+          <t>response KHÔNG chứa email/password của user; không trả 500</t>
         </is>
       </c>
       <c r="N62" s="4" t="inlineStr">
@@ -24882,7 +24882,7 @@
       </c>
       <c r="M63" s="4" t="inlineStr">
         <is>
-          <t>bang products van ton tai sau khi goi</t>
+          <t>bảng products vẫn tồn tại sau khi gọi</t>
         </is>
       </c>
       <c r="N63" s="4" t="inlineStr">
@@ -24955,7 +24955,7 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>[SEC-05] Loi SQL khong duoc tra ve HTML kem thong diep DB</t>
+          <t>[SEC-05] Lỗi SQL không được trả về HTML kèm thông điệp DB</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
@@ -24990,7 +24990,7 @@
       </c>
       <c r="M64" s="4" t="inlineStr">
         <is>
-          <t>Content-Type application/json; body khong chua &lt;h1&gt;Database Error</t>
+          <t>Content-Type application/json; body không chứa &lt;h1&gt;Database Error</t>
         </is>
       </c>
       <c r="N64" s="4" t="inlineStr">
@@ -25020,7 +25020,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>R3 - Gan sai ma SEC (SEC-02 -&gt; SEC-05). Tra ve thong diep loi SQL la he qua truc tiep cua viec noi chuoi -&gt; van la SEC-05.</t>
+          <t>R3 - Gan sai ma SEC (SEC-02 -&gt; SEC-05). Trả về thông điệp lỗi SQL là hệ quả trực tiếp của việc nối chuỗi -&gt; vẫn là SEC-05.</t>
         </is>
       </c>
       <c r="T64" s="4" t="inlineStr">
@@ -25063,7 +25063,7 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>[-] Response san pham khong duoc chua truong nam ngoai schema</t>
+          <t>[-] Response sản phẩm không được chứa trường nằm ngoài schema</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
@@ -25098,7 +25098,7 @@
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>body chi duoc chua dung 6 truong id,name,price,description,imageUrl,category_id; khong co truong noi bo nao khac</t>
+          <t>body chỉ được chứa đúng 6 trường id,name,price,description,imageUrl,category_id; không có trường nội bộ nào khác</t>
         </is>
       </c>
       <c r="N65" s="4" t="inlineStr">
@@ -25128,7 +25128,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>R3 - Gan sai ma SEC (SEC-02 -&gt; -). Xem luat R5: tham so ?debug=true khong ton tai. | R5 - Tham so bia: `?debug=true` khong ton tai trong api_specification.md lan trong server.js. AI tu nghi ra mot co debug de test. Test se 'pass' nhung khong chung minh dieu gi vi tham so bi bo qua hoan toan. DA SUA: bo tham so bia, kiem dung dieu co the kiem - response san pham khong duoc chua truong nam ngoai schema da dac ta.</t>
+          <t>R3 - Gan sai ma SEC (SEC-02 -&gt; -). Xem luật R5: tham số ?debug=true không tồn tại. | R5 - Tham số bịa: `?debug=true` không tồn tại trong api_specification.md lẫn trong server.js. AI tự nghĩ ra một cờ debug để test. Test sẽ 'pass' nhưng không chứng minh điều gì vì tham số bị bỏ qua hoàn toàn. ĐÃ SỬA: bỏ tham số bịa, kiểm đúng điều có thể kiểm - response sản phẩm không được chứa trường nằm ngoài schema đã đặc tả.</t>
         </is>
       </c>
       <c r="T65" s="4" t="inlineStr">
@@ -25171,7 +25171,7 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>[SEC-02] Tao san pham KHONG kem token</t>
+          <t>[SEC-02] Tạo sản phẩm KHÔNG kèm token</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
@@ -25206,7 +25206,7 @@
       </c>
       <c r="M66" s="4" t="inlineStr">
         <is>
-          <t>san pham KHONG duoc tao; kiem tra bang GET /api/products?search=Hacked</t>
+          <t>sản phẩm KHÔNG được tạo; kiểm tra bằng GET /api/products?search=Hacked</t>
         </is>
       </c>
       <c r="N66" s="4" t="inlineStr">
@@ -25236,7 +25236,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>R3 - Gan sai ma SEC (SEC-03 -&gt; SEC-02). Thieu JWT -&gt; SEC-02.</t>
+          <t>R3 - Gan sai ma SEC (SEC-03 -&gt; SEC-02). Thiếu JWT -&gt; SEC-02.</t>
         </is>
       </c>
       <c r="T66" s="4" t="inlineStr">
@@ -25279,7 +25279,7 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>[SEC-02] Sua san pham KHONG kem token</t>
+          <t>[SEC-02] Sửa sản phẩm KHÔNG kèm token</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
@@ -25314,7 +25314,7 @@
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>tra 403 khi token hop le nhung role != 'admin'; hanh dong admin KHONG duoc thuc hien</t>
+          <t>trả 403 khi token hợp lệ nhưng role != 'admin'; hành động admin KHÔNG được thực hiện</t>
         </is>
       </c>
       <c r="N67" s="4" t="inlineStr">
@@ -25387,7 +25387,7 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>[SEC-02] Xoa san pham KHONG kem token</t>
+          <t>[SEC-02] Xóa sản phẩm KHÔNG kèm token</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
@@ -25422,7 +25422,7 @@
       </c>
       <c r="M68" s="4" t="inlineStr">
         <is>
-          <t>san pham id=2 van con sau khi goi</t>
+          <t>sản phẩm id=2 vẫn còn sau khi gọi</t>
         </is>
       </c>
       <c r="N68" s="4" t="inlineStr">
@@ -25495,7 +25495,7 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>[SEC-02] Token sai chu ky khi tao san pham</t>
+          <t>[SEC-02] Token sai chữ ký khi tạo sản phẩm</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -25530,7 +25530,7 @@
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>tra 403 khi token hop le nhung role != 'admin'; hanh dong admin KHONG duoc thuc hien</t>
+          <t>trả 403 khi token hợp lệ nhưng role != 'admin'; hành động admin KHÔNG được thực hiện</t>
         </is>
       </c>
       <c r="N69" s="4" t="inlineStr">
@@ -25603,7 +25603,7 @@
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>[SEC-03] User thuong sua san pham cua he thong</t>
+          <t>[SEC-03] User thường sửa sản phẩm của hệ thống</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
@@ -25638,7 +25638,7 @@
       </c>
       <c r="M70" s="4" t="inlineStr">
         <is>
-          <t>payload HTML/script khong duoc luu tho; server tra ve ban da escape hoac tu choi (4xx)</t>
+          <t>payload HTML/script không được lưu thô; server trả về bản đã escape hoặc từ chối (4xx)</t>
         </is>
       </c>
       <c r="N70" s="4" t="inlineStr">
@@ -25668,7 +25668,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>R3 - Gan sai ma SEC (SEC-04 -&gt; SEC-03). User thuong sua san pham = thieu kiem role -&gt; SEC-03, khong phai SEC-04.</t>
+          <t>R3 - Gan sai ma SEC (SEC-04 -&gt; SEC-03). User thường sửa sản phẩm = thiếu kiểm role -&gt; SEC-03, không phải SEC-04.</t>
         </is>
       </c>
       <c r="T70" s="4" t="inlineStr">
@@ -25711,7 +25711,7 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>[SEC-03] User thuong (role=user) tao san pham</t>
+          <t>[SEC-03] User thường (role=user) tạo sản phẩm</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
@@ -25736,7 +25736,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>{"name":"User tao 23127060","price":5000,"category_id":1}</t>
+          <t>{"name":"User tạo 23127060","price":5000,"category_id":1}</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -25746,7 +25746,7 @@
       </c>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>chi role=admin moi duoc tao san pham</t>
+          <t>chỉ role=admin mới được tạo sản phẩm</t>
         </is>
       </c>
       <c r="N71" s="4" t="inlineStr">
@@ -25819,7 +25819,7 @@
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>[SEC-03] User thuong xoa san pham</t>
+          <t>[SEC-03] User thường xóa sản phẩm</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
@@ -25854,7 +25854,7 @@
       </c>
       <c r="M72" s="4" t="inlineStr">
         <is>
-          <t>truy van dung parameterized query: payload SQLi bi coi la chuoi tim kiem thuong, khong doi ngu nghia cau lenh; khong tra HTML loi DB</t>
+          <t>truy vấn dùng parameterized query: payload SQLi bị coi là chuỗi tìm kiếm thường, không đổi ngữ nghĩa câu lệnh; không trả HTML lỗi DB</t>
         </is>
       </c>
       <c r="N72" s="4" t="inlineStr">
@@ -25927,7 +25927,7 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>[SEC-04] Luu the script vao ten san pham roi doc lai</t>
+          <t>[SEC-04] Lưu thẻ script vào tên sản phẩm rồi đọc lại</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -25962,7 +25962,7 @@
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>bi tu choi HOAC khi GET lai phai duoc escape</t>
+          <t>bị từ chối HOẶC khi GET lại phải được escape</t>
         </is>
       </c>
       <c r="N73" s="4" t="inlineStr">
@@ -26035,7 +26035,7 @@
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>[-] Gui kem truong id de ghi de khoa chinh</t>
+          <t>[-] Gửi kèm trường id để ghi đè khóa chính</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
@@ -26060,7 +26060,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>{"id":1,"name":"Ghi de id 23127060","price":1000,"category_id":1}</t>
+          <t>{"id":1,"name":"Ghi đè id 23127060","price":1000,"category_id":1}</t>
         </is>
       </c>
       <c r="L74" s="4" t="inlineStr">
@@ -26070,7 +26070,7 @@
       </c>
       <c r="M74" s="4" t="inlineStr">
         <is>
-          <t>san pham id=1 cu KHONG bi ghi de</t>
+          <t>sản phẩm id=1 cũ KHÔNG bị ghi đè</t>
         </is>
       </c>
       <c r="N74" s="4" t="inlineStr">
@@ -26100,7 +26100,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>R3 - Gan sai ma SEC (SEC-06 -&gt; -). Ghi de khoa chinh 'id' khong phai truong 'role' nen khong thuoc SEC-06.</t>
+          <t>R3 - Gan sai ma SEC (SEC-06 -&gt; -). Ghi đè khóa chính 'id' không phải trường 'role' nên không thuộc SEC-06.</t>
         </is>
       </c>
       <c r="T74" s="4" t="inlineStr">
@@ -26143,7 +26143,7 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>[SEC-06] User thuong tu nang role='admin' roi tao san pham</t>
+          <t>[SEC-06] User thường tự nâng role='admin' rồi tạo sản phẩm</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
@@ -26178,7 +26178,7 @@
       </c>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>role sau khi goi PUT /api/users/me van phai la 'user'; POST /api/products sau do phai tra 403</t>
+          <t>role sau khi gọi PUT /api/users/me vẫn phải là 'user'; POST /api/products sau đó phải trả 403</t>
         </is>
       </c>
       <c r="N75" s="4" t="inlineStr">
@@ -26208,7 +26208,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>R3 - Gan sai ma SEC (SEC-07 -&gt; SEC-06). Da viet lai thanh chuoi leo thang quyen (xem luat R1). | R1 - Ky vong 429 khong co can cu trong SRS. DA SUA: thay bang chuoi leo thang quyen SEC-06 -&gt; SEC-03: user thuong tu nang role roi tao san pham.</t>
+          <t>R3 - Gan sai ma SEC (SEC-07 -&gt; SEC-06). Đã viết lại thành chuỗi leo thang quyền (xem luật R1). | R1 - Kỳ vọng 429 không có căn cứ trong SRS. ĐÃ SỬA: thay bằng chuỗi leo thang quyền SEC-06 -&gt; SEC-03: user thường tự nâng role rồi tạo sản phẩm.</t>
         </is>
       </c>
       <c r="T75" s="4" t="inlineStr">
@@ -26251,7 +26251,7 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>GET /api/products tra ve mang doi tuong dung schema</t>
+          <t>GET /api/products trả về mảng đối tượng đúng schema</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
@@ -26286,7 +26286,7 @@
       </c>
       <c r="M76" s="5" t="inlineStr">
         <is>
-          <t>body la array; moi phan tu co id (integer), name (string), price (number)</t>
+          <t>body là array; mỗi phần tử có id (integer), name (string), price (number)</t>
         </is>
       </c>
       <c r="N76" s="5" t="inlineStr">
@@ -26316,7 +26316,7 @@
       </c>
       <c r="S76" s="5" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T76" s="5" t="inlineStr">
@@ -26359,7 +26359,7 @@
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>GET /api/products/1 khop schema san pham don</t>
+          <t>GET /api/products/1 khớp schema sản phẩm đơn</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
@@ -26394,7 +26394,7 @@
       </c>
       <c r="M77" s="5" t="inlineStr">
         <is>
-          <t>body khop jsonSchema product_schema; additionalProperties=false</t>
+          <t>body khớp jsonSchema product_schema; additionalProperties=false</t>
         </is>
       </c>
       <c r="N77" s="5" t="inlineStr">
@@ -26424,7 +26424,7 @@
       </c>
       <c r="S77" s="5" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T77" s="5" t="inlineStr">
@@ -26467,7 +26467,7 @@
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>price luon la number ke ca voi id chan</t>
+          <t>price luôn là number kể cả với id chẵn</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -26532,7 +26532,7 @@
       </c>
       <c r="S78" s="5" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T78" s="5" t="inlineStr">
@@ -26610,7 +26610,7 @@
       </c>
       <c r="M79" s="5" t="inlineStr">
         <is>
-          <t>status 404; body khop { error: string }</t>
+          <t>status 404; body khớp { error: string }</t>
         </is>
       </c>
       <c r="N79" s="5" t="inlineStr">
@@ -26640,7 +26640,7 @@
       </c>
       <c r="S79" s="5" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T79" s="5" t="inlineStr">
@@ -26683,7 +26683,7 @@
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Response loi luon la application/json chu khong phai HTML</t>
+          <t>Response lỗi luôn là application/json chứ không phải HTML</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -26718,7 +26718,7 @@
       </c>
       <c r="M80" s="5" t="inlineStr">
         <is>
-          <t>Content-Type application/json; body khong chua &lt;h1&gt;</t>
+          <t>Content-Type application/json; body không chứa &lt;h1&gt;</t>
         </is>
       </c>
       <c r="N80" s="5" t="inlineStr">
@@ -26748,7 +26748,7 @@
       </c>
       <c r="S80" s="5" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T80" s="5" t="inlineStr">
@@ -26791,7 +26791,7 @@
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>POST thanh cong tra ve 201 va body chua id vua tao</t>
+          <t>POST thành công trả về 201 và body chứa id vừa tạo</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
@@ -26826,7 +26826,7 @@
       </c>
       <c r="M81" s="5" t="inlineStr">
         <is>
-          <t>status 201; body co id kieu integer</t>
+          <t>status 201; body có id kiểu integer</t>
         </is>
       </c>
       <c r="N81" s="5" t="inlineStr">
@@ -26856,7 +26856,7 @@
       </c>
       <c r="S81" s="5" t="inlineStr">
         <is>
-          <t>Buoc, du lieu va ky vong deu doi chieu duoc voi SRS; assertion da cu the; chay doc lap duoc sau khi _setup chay xong.</t>
+          <t>Bước, dữ liệu và kỳ vọng đều đối chiếu được với SRS; assertion đã cụ thể; chạy độc lập được sau khi _setup chạy xong.</t>
         </is>
       </c>
       <c r="T81" s="5" t="inlineStr">
@@ -26899,7 +26899,7 @@
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>Kieu cua truong price phai giong nhau giua san pham id le va id chan</t>
+          <t>Kiểu của trường price phải giống nhau giữa sản phẩm id lẻ và id chẵn</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -26914,7 +26914,7 @@
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>Da goi GET /api/products/1 truoc do va luu lai kieu cua truong price</t>
+          <t>Đã gọi GET /api/products/1 trước đó và lưu lại kiểu của trường price</t>
         </is>
       </c>
       <c r="J82" s="5" t="inlineStr">
@@ -26934,7 +26934,7 @@
       </c>
       <c r="M82" s="5" t="inlineStr">
         <is>
-          <t>typeof price cua id=2 phai bang typeof price cua id=1; ca hai deu phai la number; GET /api/products (danh sach) cung phai tra price kieu number cho MOI phan tu</t>
+          <t>typeof price của id=2 phải bằng typeof price của id=1; cả hai đều phải là number; GET /api/products (danh sách) cũng phải trả price kiểu number cho MỌI phần tử</t>
         </is>
       </c>
       <c r="N82" s="5" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="S82" s="5" t="inlineStr">
         <is>
-          <t>Case do sinh vien tu viet sau khi doc ma nguon SUT; khong qua bo sinh tu dong.</t>
+          <t>Case do sinh viên tự viết sau khi đọc mã nguồn SUT; không qua bộ sinh tự động.</t>
         </is>
       </c>
       <c r="T82" s="5" t="inlineStr">
@@ -26979,7 +26979,7 @@
       </c>
       <c r="V82" s="5" t="inlineStr">
         <is>
-          <t>API - Moi request rieng le deu hop le: `{"price": 30000000}` dung schema, va `{"price": "28000000"}` cung la mot JSON hop le. Vi pham chi hien ra khi SO SANH hai response voi nhau. Bo sinh danh gia tung case doc lap nen khong co cho nao de dat mot khang dinh bac cao hon lien ket hai request. Neu chi test id le (nhu vi du trong tai lieu hay dung) thi khong bao gio thay bug nay.</t>
+          <t>API - Mỗi request riêng lẻ đều hợp lệ: `{"price": 30000000}` đúng schema, và `{"price": "28000000"}` cũng là một JSON hợp lệ. Vi phạm chỉ hiện ra khi SO SÁNH hai response với nhau. Bộ sinh đánh giá từng case độc lập nên không có chỗ nào để đặt một khẳng định bậc cao hơn liên kết hai request. Nếu chỉ test id lẻ (như ví dụ trong tài liệu hay dùng) thì không bao giờ thấy bug này.</t>
         </is>
       </c>
     </row>
@@ -27011,7 +27011,7 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>[SEC-02] Khach vang lai xoa duoc toan bo catalog roi kiem so san pham con lai</t>
+          <t>[SEC-02] Khách vãng lai xóa được toàn bộ catalog rồi kiểm số sản phẩm còn lại</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
@@ -27026,7 +27026,7 @@
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>Da goi DELETE /api/products/:id cho ca 5 san pham seed MA KHONG kem header Authorization</t>
+          <t>Đã gọi DELETE /api/products/:id cho cả 5 sản phẩm seed MÀ KHÔNG kèm header Authorization</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
@@ -27046,7 +27046,7 @@
       </c>
       <c r="M83" s="4" t="inlineStr">
         <is>
-          <t>danh sach san pham phai con nguyen 5 phan tu vi cac lenh DELETE khong token dang le phai bi tu choi 401; neu danh sach rong thi mot nguoi khong dang nhap da xoa sach catalog</t>
+          <t>danh sách sản phẩm phải còn nguyên 5 phần tử vì các lệnh DELETE không token đáng lẽ phải bị từ chối 401; nếu danh sách rỗng thì một người không đăng nhập đã xóa sạch catalog</t>
         </is>
       </c>
       <c r="N83" s="4" t="inlineStr">
@@ -27076,7 +27076,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>Case do sinh vien tu viet sau khi doc ma nguon SUT; khong qua bo sinh tu dong.</t>
+          <t>Case do sinh viên tự viết sau khi đọc mã nguồn SUT; không qua bộ sinh tự động.</t>
         </is>
       </c>
       <c r="T83" s="4" t="inlineStr">
@@ -27091,7 +27091,7 @@
       </c>
       <c r="V83" s="4" t="inlineStr">
         <is>
-          <t>API - Bo sinh co case 'DELETE khong token -&gt; phai 401', va case do da bat duoc bug. Nhung mot dong 'expected 401, got 200' trong bao cao khong noi len duoc muc do. Case nay do HAU QUA: sau 5 request khong xac thuc thi cua hang khong con san pham nao de ban. Cung mot bug, nhung bang chung nay moi du suc thuyet phuc nguoi ra quyet dinh. Can chuoi 6 request.</t>
+          <t>API - Bộ sinh có case 'DELETE không token -&gt; phải 401', và case đó đã bắt được bug. Nhưng một dòng 'expected 401, got 200' trong báo cáo không nói lên được mức độ. Case này đo HẬU QUẢ: sau 5 request không xác thực thì cửa hàng không còn sản phẩm nào để bán. Cùng một bug, nhưng bằng chứng này mới đủ sức thuyết phục người ra quyết định. Cần chuỗi 6 request.</t>
         </is>
       </c>
     </row>
@@ -27123,7 +27123,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>PUT chi gui truong name: cac truong khong gui KHONG duoc bi ghi de thanh null</t>
+          <t>PUT chỉ gửi trường name: các trường không gửi KHÔNG được bị ghi đè thành null</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -27138,7 +27138,7 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Da tao san pham day du 5 truong, sau do goi PUT chi voi {"name": "Ten moi 23127060"}</t>
+          <t>Đã tạo sản phẩm đầy đủ 5 trường, sau đó gọi PUT chỉ với {"name": "Ten moi 23127060"}</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -27158,7 +27158,7 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>name phai la ten moi; NHUNG price, description, imageUrl, category_id phai giu nguyen gia tri cu, KHONG duoc bien thanh null; SRS FR-15: 'Khi Sua mot san pham, chi san pham do bi thay doi'</t>
+          <t>name phải là tên mới; NHƯNG price, description, imageUrl, category_id phải giữ nguyên giá trị cũ, KHÔNG được biến thành null; SRS FR-15: 'Khi Sửa một sản phẩm, chỉ sản phẩm đó bị thay đổi'</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -27188,7 +27188,7 @@
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>Case do sinh vien tu viet sau khi doc ma nguon SUT; khong qua bo sinh tu dong.</t>
+          <t>Case do sinh viên tự viết sau khi đọc mã nguồn SUT; không qua bộ sinh tự động.</t>
         </is>
       </c>
       <c r="T84" s="2" t="inlineStr">
@@ -27203,7 +27203,7 @@
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>API - Bo sinh phu tung tham so cua PUT mot cach doc lap: gui name sai, gui price sai... Moi case deu gui DU 5 truong roi doi mot truong. Khong case nao gui THIEU truong, vi 'thieu truong' duoc coi la lop khong hop le cua chinh truong do chu khong phai mot phep thu ve hanh vi cap nhat mot phan. Can chuoi POST -&gt; PUT -&gt; GET moi thay duoc 4 truong con lai da bi xoa trang.</t>
+          <t>API - Bộ sinh phủ từng tham số của PUT một cách độc lập: gửi name sai, gửi price sai... Mọi case đều gửi ĐỦ 5 trường rồi đổi một trường. Không case nào gửi THIẾU trường, vì 'thiếu trường' được coi là lớp không hợp lệ của chính trường đó chứ không phải một phép thử về hành vi cập nhật một phần. Cần chuỗi POST -&gt; PUT -&gt; GET mới thấy được 4 trường còn lại đã bị xóa trắng.</t>
         </is>
       </c>
     </row>
@@ -27235,7 +27235,7 @@
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>Response loi phai la application/json, khong duoc la HTML</t>
+          <t>Response lỗi phải là application/json, không được là HTML</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
@@ -27270,7 +27270,7 @@
       </c>
       <c r="M85" s="5" t="inlineStr">
         <is>
-          <t>header Content-Type phai chua 'application/json'; body phai parse duoc thanh JSON co truong error; body KHONG duoc chua the HTML nao (&lt;h1&gt;, &lt;p&gt;); khong duoc lo thong diep loi cua tang CSDL</t>
+          <t>header Content-Type phải chứa 'application/json'; body phải parse được thành JSON có trường error; body KHÔNG được chứa thẻ HTML nào (&lt;h1&gt;, &lt;p&gt;); không được lộ thông điệp lỗi của tầng CSDL</t>
         </is>
       </c>
       <c r="N85" s="5" t="inlineStr">
@@ -27300,7 +27300,7 @@
       </c>
       <c r="S85" s="5" t="inlineStr">
         <is>
-          <t>Case do sinh vien tu viet sau khi doc ma nguon SUT; khong qua bo sinh tu dong.</t>
+          <t>Case do sinh viên tự viết sau khi đọc mã nguồn SUT; không qua bộ sinh tự động.</t>
         </is>
       </c>
       <c r="T85" s="5" t="inlineStr">
@@ -27315,7 +27315,7 @@
       </c>
       <c r="V85" s="5" t="inlineStr">
         <is>
-          <t>MODEL - Bo sinh mac dinh moi response cua mot REST API deu la JSON, nen no khang dinh len NOI DUNG body ma khong bao gio khang dinh len HEADER Content-Type. Khi SUT tra ve HTML, buoc pm.response.json() nem loi va test that bai voi thong bao 'Unexpected token &lt;' - mot loi trong dan den chan doan sai la 'test bi hong' chu khong phai 'API vi pham hop dong'. Phai kiem Content-Type TRUOC khi parse.</t>
+          <t>MODEL - Bộ sinh mặc định mọi response của một REST API đều là JSON, nên nó khẳng định lên NỘI DUNG body mà không bao giờ khẳng định lên HEADER Content-Type. Khi SUT trả về HTML, bước pm.response.json() ném lỗi và test thất bại với thông báo 'Unexpected token &lt;' - một lỗi trông dẫn đến chẩn đoán sai là 'test bị hỏng' chứ không phải 'API vi phạm hợp đồng'. Phải kiểm Content-Type TRƯỚC khi parse.</t>
         </is>
       </c>
     </row>
@@ -27347,7 +27347,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Tao san pham voi category_id khong ton tai roi doi chieu voi danh sach danh muc</t>
+          <t>Tạo sản phẩm với category_id không tồn tại rồi đối chiếu với danh sách danh mục</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -27382,7 +27382,7 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>danh sach danh muc chi co id 1, 2, 3; san pham vua tao tro toi category_id = 9999 la mot tham chieu treo; SRS FR-15: 'Danh muc: bat buoc, phai chon tu danh sach co san'</t>
+          <t>danh sách danh mục chỉ có id 1, 2, 3; sản phẩm vừa tạo trỏ tới category_id = 9999 là một tham chiếu treo; SRS FR-15: 'Danh mục: bắt buộc, phải chọn từ danh sách có sẵn'</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -27412,7 +27412,7 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>Case do sinh vien tu viet sau khi doc ma nguon SUT; khong qua bo sinh tu dong.</t>
+          <t>Case do sinh viên tự viết sau khi đọc mã nguồn SUT; không qua bộ sinh tự động.</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
@@ -27427,7 +27427,7 @@
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>API - Bo sinh co case 'category_id = 9999 phai bi tu choi'. Nhung de CHUNG MINH day la tham chieu treo chu khong phai mot danh muc that ma minh khong biet, phai doc bang categories bang mot request thu hai. Rang buoc toan ven tham chieu ve ban chat noi ve QUAN HE giua hai tai nguyen, khong the kiem trong pham vi mot request.</t>
+          <t>API - Bộ sinh có case 'category_id = 9999 phải bị từ chối'. Nhưng để CHỨNG MINH đây là tham chiếu treo chứ không phải một danh mục thật mà mình không biết, phải đọc bảng categories bằng một request thứ hai. Ràng buộc toàn vẹn tham chiếu về bản chất nói về QUAN HỆ giữa hai tài nguyên, không thể kiểm trong phạm vi một request.</t>
         </is>
       </c>
     </row>
@@ -27459,7 +27459,7 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>[SEC-05] UNION SELECT qua ?search doc duoc mat khau plaintext trong bang users</t>
+          <t>[SEC-05] UNION SELECT qua ?search đọc được mật khẩu plaintext trong bảng users</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
@@ -27494,7 +27494,7 @@
       </c>
       <c r="M87" s="4" t="inlineStr">
         <is>
-          <t>ket qua tra ve chi duoc chua san pham, KHONG duoc chua chuoi '@eshop.com' hay 'Admin123!'; so cot cua products (5) trung voi so cot chon tu users nen UNION ghep duoc - day la dieu Parameterized Query (SEC-05) ngan chan</t>
+          <t>kết quả trả về chỉ được chứa sản phẩm, KHÔNG được chứa chuỗi '@eshop.com' hay 'Admin123!'; số cột của products (5) trùng với số cột chọn từ users nên UNION ghép được - đây là điều Parameterized Query (SEC-05) ngăn chặn</t>
         </is>
       </c>
       <c r="N87" s="4" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>Case do sinh vien tu viet sau khi doc ma nguon SUT; khong qua bo sinh tu dong.</t>
+          <t>Case do sinh viên tự viết sau khi đọc mã nguồn SUT; không qua bộ sinh tự động.</t>
         </is>
       </c>
       <c r="T87" s="4" t="inlineStr">
@@ -27539,7 +27539,7 @@
       </c>
       <c r="V87" s="4" t="inlineStr">
         <is>
-          <t>API - Bo sinh co payload UNION SELECT nhung viet chung chung voi 5 cot tuy y. UNION trong SQLite chi chay khi SO COT KHOP CHINH XAC; doan sai so cot thi chi nhan duoc loi va ket luan nham la 'da duoc bao ve'. Phai doc database.js dem dung 5 cot cua bang products roi chon dung 5 cot tu users. Do la buoc trinh sat lay tu MA NGUON, khong the suy ra tu dac ta.</t>
+          <t>API - Bộ sinh có payload UNION SELECT nhưng viết chung chung với 5 cột tùy ý. UNION trong SQLite chỉ chạy khi SỐ CỘT KHỚP CHÍNH XÁC; đoán sai số cột thì chỉ nhận được lỗi và kết luận nhầm là 'đã được bảo vệ'. Phải đọc database.js đếm đúng 5 cột của bảng products rồi chọn đúng 5 cột từ users. Đó là bước trinh sát lấy từ MÃ NGUỒN, không thể suy ra từ đặc tả.</t>
         </is>
       </c>
     </row>
